--- a/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
+++ b/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BC653B-103B-40AD-918D-A2CC11AC8500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C86845-FD20-4D07-AA56-0D5F9BD38B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -808,6 +808,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -820,6 +847,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -833,36 +863,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -939,8 +939,8 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FF65D5CD"/>
       <color rgb="FF42ACD2"/>
-      <color rgb="FF65D5CD"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1144,62 +1144,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
     </row>
     <row r="2" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
-      <c r="V2" s="56"/>
-      <c r="W2" s="56"/>
-      <c r="X2" s="56"/>
-      <c r="Y2" s="56"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="54"/>
+      <c r="X2" s="54"/>
+      <c r="Y2" s="54"/>
     </row>
     <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1207,37 +1207,37 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="45" t="s">
+      <c r="E4" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="45"/>
-      <c r="G4" s="46" t="s">
+      <c r="F4" s="55"/>
+      <c r="G4" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="47" t="s">
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="48" t="s">
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="49" t="s">
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
+      <c r="U4" s="58"/>
+      <c r="V4" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="W4" s="49"/>
-      <c r="X4" s="49"/>
-      <c r="Y4" s="49"/>
+      <c r="W4" s="59"/>
+      <c r="X4" s="59"/>
+      <c r="Y4" s="59"/>
     </row>
     <row r="5" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1317,12 +1317,12 @@
       </c>
     </row>
     <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
       <c r="E6" s="7" t="s">
         <v>31</v>
       </c>
@@ -1388,12 +1388,12 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
       <c r="E7" s="11" t="s">
         <v>31</v>
       </c>
@@ -1447,33 +1447,33 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="42"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="42"/>
-      <c r="R8" s="42"/>
-      <c r="S8" s="42"/>
-      <c r="T8" s="42"/>
-      <c r="U8" s="42"/>
-      <c r="V8" s="42"/>
-      <c r="W8" s="42"/>
-      <c r="X8" s="42"/>
-      <c r="Y8" s="42"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="51"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="51"/>
+      <c r="R8" s="51"/>
+      <c r="S8" s="51"/>
+      <c r="T8" s="51"/>
+      <c r="U8" s="51"/>
+      <c r="V8" s="51"/>
+      <c r="W8" s="51"/>
+      <c r="X8" s="51"/>
+      <c r="Y8" s="51"/>
     </row>
     <row r="9" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
@@ -1526,7 +1526,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="26"/>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="39" t="s">
         <v>54</v>
       </c>
       <c r="G10" s="19"/>
@@ -1587,33 +1587,33 @@
       <c r="Y11" s="20"/>
     </row>
     <row r="12" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="43"/>
-      <c r="Y12" s="43"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="52"/>
+      <c r="O12" s="52"/>
+      <c r="P12" s="52"/>
+      <c r="Q12" s="52"/>
+      <c r="R12" s="52"/>
+      <c r="S12" s="52"/>
+      <c r="T12" s="52"/>
+      <c r="U12" s="52"/>
+      <c r="V12" s="52"/>
+      <c r="W12" s="52"/>
+      <c r="X12" s="52"/>
+      <c r="Y12" s="52"/>
     </row>
     <row r="13" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
@@ -1629,7 +1629,7 @@
         <v>3.5</v>
       </c>
       <c r="E13" s="20"/>
-      <c r="F13" s="57" t="s">
+      <c r="F13" s="41" t="s">
         <v>54</v>
       </c>
       <c r="G13" s="29"/>
@@ -1838,33 +1838,33 @@
       <c r="Y18" s="20"/>
     </row>
     <row r="19" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+      <c r="A19" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="50"/>
-      <c r="P19" s="50"/>
-      <c r="Q19" s="50"/>
-      <c r="R19" s="50"/>
-      <c r="S19" s="50"/>
-      <c r="T19" s="50"/>
-      <c r="U19" s="50"/>
-      <c r="V19" s="50"/>
-      <c r="W19" s="50"/>
-      <c r="X19" s="50"/>
-      <c r="Y19" s="50"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="44"/>
+      <c r="S19" s="44"/>
+      <c r="T19" s="44"/>
+      <c r="U19" s="44"/>
+      <c r="V19" s="44"/>
+      <c r="W19" s="44"/>
+      <c r="X19" s="44"/>
+      <c r="Y19" s="44"/>
     </row>
     <row r="20" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
@@ -1945,22 +1945,22 @@
         <v>12</v>
       </c>
       <c r="B22" s="32"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
       <c r="I22" s="21"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="58"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
       <c r="N22" s="21"/>
-      <c r="O22" s="58"/>
-      <c r="P22" s="58"/>
-      <c r="Q22" s="58"/>
-      <c r="R22" s="58"/>
+      <c r="O22" s="42"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="42"/>
+      <c r="R22" s="42"/>
       <c r="S22" s="21"/>
       <c r="T22" s="22"/>
       <c r="U22" s="22"/>
@@ -1970,33 +1970,33 @@
       <c r="Y22" s="34"/>
     </row>
     <row r="23" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="55"/>
-      <c r="K23" s="55"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="55"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="55"/>
-      <c r="P23" s="55"/>
-      <c r="Q23" s="55"/>
-      <c r="R23" s="55"/>
-      <c r="S23" s="55"/>
-      <c r="T23" s="55"/>
-      <c r="U23" s="55"/>
-      <c r="V23" s="55"/>
-      <c r="W23" s="55"/>
-      <c r="X23" s="55"/>
-      <c r="Y23" s="55"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
+      <c r="K23" s="49"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="49"/>
+      <c r="N23" s="49"/>
+      <c r="O23" s="49"/>
+      <c r="P23" s="49"/>
+      <c r="Q23" s="49"/>
+      <c r="R23" s="49"/>
+      <c r="S23" s="49"/>
+      <c r="T23" s="49"/>
+      <c r="U23" s="49"/>
+      <c r="V23" s="49"/>
+      <c r="W23" s="49"/>
+      <c r="X23" s="49"/>
+      <c r="Y23" s="49"/>
     </row>
     <row r="24" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
@@ -2043,59 +2043,59 @@
       <c r="C25" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="59">
+      <c r="D25" s="43">
         <v>1</v>
       </c>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
       <c r="I25" s="21"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="42"/>
       <c r="N25" s="21"/>
-      <c r="O25" s="58"/>
-      <c r="P25" s="58"/>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="58"/>
+      <c r="O25" s="42"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="42"/>
+      <c r="R25" s="42"/>
       <c r="S25" s="21"/>
       <c r="T25" s="22"/>
       <c r="U25" s="22"/>
-      <c r="V25" s="58"/>
-      <c r="W25" s="58"/>
+      <c r="V25" s="42"/>
+      <c r="W25" s="42"/>
       <c r="X25" s="21"/>
-      <c r="Y25" s="58"/>
+      <c r="Y25" s="42"/>
     </row>
     <row r="26" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="52"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="52"/>
-      <c r="K26" s="52"/>
-      <c r="L26" s="52"/>
-      <c r="M26" s="52"/>
-      <c r="N26" s="52"/>
-      <c r="O26" s="52"/>
-      <c r="P26" s="52"/>
-      <c r="Q26" s="52"/>
-      <c r="R26" s="52"/>
-      <c r="S26" s="52"/>
-      <c r="T26" s="52"/>
-      <c r="U26" s="52"/>
-      <c r="V26" s="52"/>
-      <c r="W26" s="52"/>
-      <c r="X26" s="52"/>
-      <c r="Y26" s="52"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="46"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="X26" s="46"/>
+      <c r="Y26" s="46"/>
     </row>
     <row r="27" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
@@ -2167,66 +2167,61 @@
       <c r="Y28" s="1"/>
     </row>
     <row r="30" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="53"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="53"/>
-      <c r="I30" s="53"/>
-      <c r="J30" s="53"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="53"/>
-      <c r="M30" s="53"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="53"/>
-      <c r="P30" s="53"/>
-      <c r="Q30" s="53"/>
-      <c r="R30" s="53"/>
-      <c r="S30" s="53"/>
-      <c r="T30" s="53"/>
-      <c r="U30" s="53"/>
-      <c r="V30" s="53"/>
-      <c r="W30" s="53"/>
-      <c r="X30" s="53"/>
-      <c r="Y30" s="53"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="47"/>
+      <c r="K30" s="47"/>
+      <c r="L30" s="47"/>
+      <c r="M30" s="47"/>
+      <c r="N30" s="47"/>
+      <c r="O30" s="47"/>
+      <c r="P30" s="47"/>
+      <c r="Q30" s="47"/>
+      <c r="R30" s="47"/>
+      <c r="S30" s="47"/>
+      <c r="T30" s="47"/>
+      <c r="U30" s="47"/>
+      <c r="V30" s="47"/>
+      <c r="W30" s="47"/>
+      <c r="X30" s="47"/>
+      <c r="Y30" s="47"/>
     </row>
     <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="54"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="54"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="54"/>
-      <c r="L31" s="54"/>
-      <c r="M31" s="54"/>
-      <c r="N31" s="54"/>
-      <c r="O31" s="54"/>
-      <c r="P31" s="54"/>
-      <c r="Q31" s="54"/>
-      <c r="R31" s="54"/>
-      <c r="S31" s="54"/>
-      <c r="T31" s="54"/>
-      <c r="U31" s="54"/>
-      <c r="V31" s="54"/>
-      <c r="W31" s="54"/>
-      <c r="X31" s="54"/>
-      <c r="Y31" s="54"/>
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="48"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="48"/>
+      <c r="O31" s="48"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="48"/>
+      <c r="R31" s="48"/>
+      <c r="S31" s="48"/>
+      <c r="T31" s="48"/>
+      <c r="U31" s="48"/>
+      <c r="V31" s="48"/>
+      <c r="W31" s="48"/>
+      <c r="X31" s="48"/>
+      <c r="Y31" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A19:Y19"/>
-    <mergeCell ref="A26:Y26"/>
-    <mergeCell ref="A30:Y30"/>
-    <mergeCell ref="A31:Y31"/>
-    <mergeCell ref="A23:Y23"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A8:Y8"/>
@@ -2238,6 +2233,11 @@
     <mergeCell ref="L4:P4"/>
     <mergeCell ref="Q4:U4"/>
     <mergeCell ref="V4:Y4"/>
+    <mergeCell ref="A19:Y19"/>
+    <mergeCell ref="A26:Y26"/>
+    <mergeCell ref="A30:Y30"/>
+    <mergeCell ref="A31:Y31"/>
+    <mergeCell ref="A23:Y23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
+++ b/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C86845-FD20-4D07-AA56-0D5F9BD38B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A2DA35-0E82-41A6-8A45-0E9F12FBC7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="80">
   <si>
     <t>23–24 avr</t>
   </si>
@@ -302,20 +302,20 @@
     <t>VISITES</t>
   </si>
   <si>
-    <t>Visite du 1er (à planifier)</t>
-  </si>
-  <si>
     <t>Web app Streamlit - Total : 90h</t>
   </si>
   <si>
     <t>TPI - Serial Guard v2  |  Planning initial</t>
+  </si>
+  <si>
+    <t>Visite du 2ème expert (Dimirios Lymberis) le jeudi 7 mai à 9h</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -405,13 +405,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF6C3483"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -432,6 +425,19 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1E2A38"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -568,12 +574,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD7BDE2"/>
-        <bgColor rgb="FFCCCCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD4AC0D"/>
         <bgColor rgb="FFFF9900"/>
       </patternFill>
@@ -624,6 +624,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF42ACD2"/>
         <bgColor rgb="FFA9D4E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7BDE2"/>
+        <bgColor rgb="FFF8F8F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -706,7 +712,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -755,9 +761,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -784,31 +787,28 @@
     <xf numFmtId="0" fontId="10" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -817,24 +817,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -863,6 +846,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -939,8 +949,10 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FFD7BDE2"/>
+      <color rgb="FF42ACD2"/>
       <color rgb="FF65D5CD"/>
-      <color rgb="FF42ACD2"/>
+      <color rgb="FFF4F9FF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1144,62 +1156,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
+      <c r="A1" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
     </row>
     <row r="2" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="54" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="54"/>
-      <c r="S2" s="54"/>
-      <c r="T2" s="54"/>
-      <c r="U2" s="54"/>
-      <c r="V2" s="54"/>
-      <c r="W2" s="54"/>
-      <c r="X2" s="54"/>
-      <c r="Y2" s="54"/>
+      <c r="A2" s="47" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="47"/>
+      <c r="Y2" s="47"/>
     </row>
     <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1207,37 +1219,37 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="55" t="s">
+      <c r="E4" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="56" t="s">
+      <c r="F4" s="48"/>
+      <c r="G4" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="57" t="s">
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
-      <c r="P4" s="57"/>
-      <c r="Q4" s="58" t="s">
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="50"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="58"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="58"/>
-      <c r="U4" s="58"/>
-      <c r="V4" s="59" t="s">
+      <c r="R4" s="51"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="51"/>
+      <c r="V4" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="W4" s="59"/>
-      <c r="X4" s="59"/>
-      <c r="Y4" s="59"/>
+      <c r="W4" s="52"/>
+      <c r="X4" s="52"/>
+      <c r="Y4" s="52"/>
     </row>
     <row r="5" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1317,12 +1329,12 @@
       </c>
     </row>
     <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
       <c r="E6" s="7" t="s">
         <v>31</v>
       </c>
@@ -1388,12 +1400,12 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
       <c r="E7" s="11" t="s">
         <v>31</v>
       </c>
@@ -1447,33 +1459,33 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="51"/>
-      <c r="S8" s="51"/>
-      <c r="T8" s="51"/>
-      <c r="U8" s="51"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="44"/>
+      <c r="R8" s="44"/>
+      <c r="S8" s="44"/>
+      <c r="T8" s="44"/>
+      <c r="U8" s="44"/>
+      <c r="V8" s="44"/>
+      <c r="W8" s="44"/>
+      <c r="X8" s="44"/>
+      <c r="Y8" s="44"/>
     </row>
     <row r="9" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
@@ -1488,66 +1500,66 @@
       <c r="D9" s="17">
         <v>5</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="40"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="20"/>
-      <c r="W9" s="20"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="20"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="19"/>
     </row>
     <row r="10" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="23">
+      <c r="A10" s="22">
         <v>2</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="24">
         <v>6</v>
       </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="39" t="s">
+      <c r="E10" s="25"/>
+      <c r="F10" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="21"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="21"/>
-      <c r="Y10" s="26"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="21"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="25"/>
     </row>
     <row r="11" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
@@ -1562,64 +1574,64 @@
       <c r="D11" s="17">
         <v>7</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="18" t="s">
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="21"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="20"/>
-      <c r="W11" s="20"/>
-      <c r="X11" s="21"/>
-      <c r="Y11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="21"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="19"/>
     </row>
     <row r="12" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="52"/>
-      <c r="O12" s="52"/>
-      <c r="P12" s="52"/>
-      <c r="Q12" s="52"/>
-      <c r="R12" s="52"/>
-      <c r="S12" s="52"/>
-      <c r="T12" s="52"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="52"/>
-      <c r="W12" s="52"/>
-      <c r="X12" s="52"/>
-      <c r="Y12" s="52"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="45"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="45"/>
+      <c r="T12" s="45"/>
+      <c r="U12" s="45"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="45"/>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="45"/>
     </row>
     <row r="13" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>4</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C13" s="16" t="s">
@@ -1628,72 +1640,72 @@
       <c r="D13" s="17">
         <v>3.5</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="41" t="s">
+      <c r="E13" s="19"/>
+      <c r="F13" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="22"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="20"/>
-      <c r="W13" s="20"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="20"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="19"/>
     </row>
     <row r="14" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="23">
+      <c r="A14" s="22">
         <v>5</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="24">
         <v>4</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="28" t="s">
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="L14" s="29"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="26"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="26"/>
-      <c r="W14" s="26"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="26"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="25"/>
     </row>
     <row r="15" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>6</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="16" t="s">
@@ -1702,35 +1714,35 @@
       <c r="D15" s="17">
         <v>5.5</v>
       </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="28" t="s">
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="29"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="22"/>
-      <c r="V15" s="20"/>
-      <c r="W15" s="20"/>
-      <c r="X15" s="21"/>
-      <c r="Y15" s="20"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="19"/>
+      <c r="X15" s="20"/>
+      <c r="Y15" s="19"/>
     </row>
     <row r="16" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>7</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C16" s="16" t="s">
@@ -1739,72 +1751,72 @@
       <c r="D16" s="17">
         <v>7</v>
       </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="28" t="s">
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="N16" s="21"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="21"/>
-      <c r="T16" s="22"/>
-      <c r="U16" s="22"/>
-      <c r="V16" s="20"/>
-      <c r="W16" s="20"/>
-      <c r="X16" s="21"/>
-      <c r="Y16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="19"/>
+      <c r="W16" s="19"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="19"/>
     </row>
     <row r="17" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23">
+      <c r="A17" s="22">
         <v>8</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="24">
         <v>7</v>
       </c>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="28" t="s">
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="29"/>
-      <c r="R17" s="29"/>
-      <c r="S17" s="21"/>
-      <c r="T17" s="22"/>
-      <c r="U17" s="22"/>
-      <c r="V17" s="26"/>
-      <c r="W17" s="26"/>
-      <c r="X17" s="21"/>
-      <c r="Y17" s="26"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="21"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="25"/>
     </row>
     <row r="18" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>9</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C18" s="16" t="s">
@@ -1813,64 +1825,64 @@
       <c r="D18" s="17">
         <v>7.5</v>
       </c>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="28" t="s">
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="S18" s="21"/>
-      <c r="T18" s="22"/>
-      <c r="U18" s="22"/>
-      <c r="V18" s="29"/>
-      <c r="W18" s="29"/>
-      <c r="X18" s="21"/>
-      <c r="Y18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="21"/>
+      <c r="V18" s="28"/>
+      <c r="W18" s="28"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="44"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="44"/>
-      <c r="R19" s="44"/>
-      <c r="S19" s="44"/>
-      <c r="T19" s="44"/>
-      <c r="U19" s="44"/>
-      <c r="V19" s="44"/>
-      <c r="W19" s="44"/>
-      <c r="X19" s="44"/>
-      <c r="Y19" s="44"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="53"/>
+      <c r="P19" s="53"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="53"/>
+      <c r="S19" s="53"/>
+      <c r="T19" s="53"/>
+      <c r="U19" s="53"/>
+      <c r="V19" s="53"/>
+      <c r="W19" s="53"/>
+      <c r="X19" s="53"/>
+      <c r="Y19" s="53"/>
     </row>
     <row r="20" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>10</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="30" t="s">
         <v>68</v>
       </c>
       <c r="C20" s="16" t="s">
@@ -1879,229 +1891,230 @@
       <c r="D20" s="17">
         <v>4.5</v>
       </c>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="21"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="21"/>
-      <c r="T20" s="22"/>
-      <c r="U20" s="22"/>
-      <c r="V20" s="33" t="s">
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="21"/>
+      <c r="V20" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="W20" s="34"/>
-      <c r="X20" s="21"/>
-      <c r="Y20" s="20"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="19"/>
     </row>
     <row r="21" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="23">
+      <c r="A21" s="22">
         <v>11</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="24">
         <v>9</v>
       </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="26"/>
-      <c r="Q21" s="26"/>
-      <c r="R21" s="26"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="22"/>
-      <c r="U21" s="22"/>
-      <c r="V21" s="33" t="s">
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="21"/>
+      <c r="U21" s="21"/>
+      <c r="V21" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="W21" s="34"/>
-      <c r="X21" s="21"/>
-      <c r="Y21" s="34"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="32"/>
     </row>
     <row r="22" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23">
+      <c r="A22" s="22">
         <v>12</v>
       </c>
-      <c r="B22" s="32"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="42"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="21"/>
-      <c r="O22" s="42"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="42"/>
-      <c r="R22" s="42"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="22"/>
-      <c r="U22" s="22"/>
-      <c r="V22" s="33"/>
-      <c r="W22" s="34"/>
-      <c r="X22" s="21"/>
-      <c r="Y22" s="34"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="40"/>
+      <c r="P22" s="40"/>
+      <c r="Q22" s="40"/>
+      <c r="R22" s="40"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="21"/>
+      <c r="U22" s="21"/>
+      <c r="V22" s="40"/>
+      <c r="W22" s="40"/>
+      <c r="X22" s="20"/>
+      <c r="Y22" s="40"/>
     </row>
     <row r="23" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
-      <c r="L23" s="49"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="49"/>
-      <c r="O23" s="49"/>
-      <c r="P23" s="49"/>
-      <c r="Q23" s="49"/>
-      <c r="R23" s="49"/>
-      <c r="S23" s="49"/>
-      <c r="T23" s="49"/>
-      <c r="U23" s="49"/>
-      <c r="V23" s="49"/>
-      <c r="W23" s="49"/>
-      <c r="X23" s="49"/>
-      <c r="Y23" s="49"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="58"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="58"/>
+      <c r="O23" s="58"/>
+      <c r="P23" s="58"/>
+      <c r="Q23" s="58"/>
+      <c r="R23" s="58"/>
+      <c r="S23" s="58"/>
+      <c r="T23" s="58"/>
+      <c r="U23" s="58"/>
+      <c r="V23" s="58"/>
+      <c r="W23" s="58"/>
+      <c r="X23" s="58"/>
+      <c r="Y23" s="58"/>
     </row>
     <row r="24" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>13</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" s="25">
+      <c r="C24" s="59" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="24">
         <v>1</v>
       </c>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="21"/>
-      <c r="O24" s="26"/>
-      <c r="P24" s="26"/>
-      <c r="Q24" s="26"/>
-      <c r="R24" s="26"/>
-      <c r="S24" s="21"/>
-      <c r="T24" s="22"/>
-      <c r="U24" s="22"/>
-      <c r="V24" s="20"/>
-      <c r="W24" s="20"/>
-      <c r="X24" s="21"/>
-      <c r="Y24" s="20"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="20"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="21"/>
+      <c r="U24" s="21"/>
+      <c r="V24" s="19"/>
+      <c r="W24" s="19"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="19"/>
     </row>
     <row r="25" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>14</v>
       </c>
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="43">
+      <c r="C25" s="59" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="41">
         <v>1</v>
       </c>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="42"/>
-      <c r="K25" s="42"/>
-      <c r="L25" s="42"/>
-      <c r="M25" s="42"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="42"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="42"/>
-      <c r="R25" s="42"/>
-      <c r="S25" s="21"/>
-      <c r="T25" s="22"/>
-      <c r="U25" s="22"/>
-      <c r="V25" s="42"/>
-      <c r="W25" s="42"/>
-      <c r="X25" s="21"/>
-      <c r="Y25" s="42"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="40"/>
+      <c r="M25" s="40"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="61" t="s">
+        <v>54</v>
+      </c>
+      <c r="P25" s="40"/>
+      <c r="Q25" s="40"/>
+      <c r="R25" s="40"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="21"/>
+      <c r="U25" s="21"/>
+      <c r="V25" s="40"/>
+      <c r="W25" s="40"/>
+      <c r="X25" s="20"/>
+      <c r="Y25" s="40"/>
     </row>
     <row r="26" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
-      <c r="O26" s="46"/>
-      <c r="P26" s="46"/>
-      <c r="Q26" s="46"/>
-      <c r="R26" s="46"/>
-      <c r="S26" s="46"/>
-      <c r="T26" s="46"/>
-      <c r="U26" s="46"/>
-      <c r="V26" s="46"/>
-      <c r="W26" s="46"/>
-      <c r="X26" s="46"/>
-      <c r="Y26" s="46"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="55"/>
+      <c r="J26" s="55"/>
+      <c r="K26" s="55"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="55"/>
+      <c r="N26" s="55"/>
+      <c r="O26" s="55"/>
+      <c r="P26" s="55"/>
+      <c r="Q26" s="55"/>
+      <c r="R26" s="55"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="55"/>
+      <c r="U26" s="55"/>
+      <c r="V26" s="55"/>
+      <c r="W26" s="55"/>
+      <c r="X26" s="55"/>
+      <c r="Y26" s="55"/>
     </row>
     <row r="27" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>15</v>
       </c>
-      <c r="B27" s="35" t="s">
+      <c r="B27" s="33" t="s">
         <v>73</v>
       </c>
       <c r="C27" s="16" t="s">
@@ -2110,37 +2123,37 @@
       <c r="D27" s="17">
         <v>22</v>
       </c>
-      <c r="E27" s="36" t="s">
+      <c r="E27" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="37"/>
-      <c r="L27" s="37"/>
-      <c r="M27" s="37"/>
-      <c r="N27" s="21"/>
-      <c r="O27" s="37"/>
-      <c r="P27" s="37"/>
-      <c r="Q27" s="37"/>
-      <c r="R27" s="37"/>
-      <c r="S27" s="21"/>
-      <c r="T27" s="22"/>
-      <c r="U27" s="22"/>
-      <c r="V27" s="37"/>
-      <c r="W27" s="37"/>
-      <c r="X27" s="21"/>
-      <c r="Y27" s="37"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="35"/>
+      <c r="R27" s="35"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="21"/>
+      <c r="U27" s="21"/>
+      <c r="V27" s="35"/>
+      <c r="W27" s="35"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="35"/>
     </row>
     <row r="28" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="38"/>
-      <c r="B28" s="38" t="s">
+      <c r="A28" s="36"/>
+      <c r="B28" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38">
+      <c r="C28" s="36"/>
+      <c r="D28" s="36">
         <f>SUM(D8:D27)</f>
         <v>90</v>
       </c>
@@ -2167,61 +2180,66 @@
       <c r="Y28" s="1"/>
     </row>
     <row r="30" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="47"/>
-      <c r="P30" s="47"/>
-      <c r="Q30" s="47"/>
-      <c r="R30" s="47"/>
-      <c r="S30" s="47"/>
-      <c r="T30" s="47"/>
-      <c r="U30" s="47"/>
-      <c r="V30" s="47"/>
-      <c r="W30" s="47"/>
-      <c r="X30" s="47"/>
-      <c r="Y30" s="47"/>
+      <c r="A30" s="56"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="56"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="56"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="56"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="56"/>
+      <c r="R30" s="56"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="56"/>
+      <c r="U30" s="56"/>
+      <c r="V30" s="56"/>
+      <c r="W30" s="56"/>
+      <c r="X30" s="56"/>
+      <c r="Y30" s="56"/>
     </row>
     <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="48"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="48"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="48"/>
-      <c r="O31" s="48"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="48"/>
-      <c r="R31" s="48"/>
-      <c r="S31" s="48"/>
-      <c r="T31" s="48"/>
-      <c r="U31" s="48"/>
-      <c r="V31" s="48"/>
-      <c r="W31" s="48"/>
-      <c r="X31" s="48"/>
-      <c r="Y31" s="48"/>
+      <c r="A31" s="57"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="57"/>
+      <c r="O31" s="57"/>
+      <c r="P31" s="57"/>
+      <c r="Q31" s="57"/>
+      <c r="R31" s="57"/>
+      <c r="S31" s="57"/>
+      <c r="T31" s="57"/>
+      <c r="U31" s="57"/>
+      <c r="V31" s="57"/>
+      <c r="W31" s="57"/>
+      <c r="X31" s="57"/>
+      <c r="Y31" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A19:Y19"/>
+    <mergeCell ref="A26:Y26"/>
+    <mergeCell ref="A30:Y30"/>
+    <mergeCell ref="A31:Y31"/>
+    <mergeCell ref="A23:Y23"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A8:Y8"/>
@@ -2233,11 +2251,6 @@
     <mergeCell ref="L4:P4"/>
     <mergeCell ref="Q4:U4"/>
     <mergeCell ref="V4:Y4"/>
-    <mergeCell ref="A19:Y19"/>
-    <mergeCell ref="A26:Y26"/>
-    <mergeCell ref="A30:Y30"/>
-    <mergeCell ref="A31:Y31"/>
-    <mergeCell ref="A23:Y23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
+++ b/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A2DA35-0E82-41A6-8A45-0E9F12FBC7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7D5259-5917-4CD4-8F63-18EBA4CFADBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planning Gantt" sheetId="1" r:id="rId1"/>
@@ -439,7 +439,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -550,12 +550,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBAECE8"/>
-        <bgColor rgb="FFB3E5FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF4F9FF"/>
         <bgColor rgb="FFF8F8F8"/>
       </patternFill>
@@ -630,6 +624,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD7BDE2"/>
         <bgColor rgb="FFF8F8F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3EFEC"/>
+        <bgColor rgb="FFB3E5FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42ACD2"/>
+        <bgColor rgb="FFA8D8EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -712,7 +718,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -763,52 +769,48 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -817,7 +819,21 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -848,32 +864,23 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -949,9 +956,10 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FF42ACD2"/>
+      <color rgb="FFC3EFEC"/>
+      <color rgb="FF65D5CD"/>
       <color rgb="FFD7BDE2"/>
-      <color rgb="FF42ACD2"/>
-      <color rgb="FF65D5CD"/>
       <color rgb="FFF4F9FF"/>
     </mruColors>
   </colors>
@@ -1156,62 +1164,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
     </row>
     <row r="2" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
-      <c r="W2" s="47"/>
-      <c r="X2" s="47"/>
-      <c r="Y2" s="47"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
     </row>
     <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1219,37 +1227,37 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="48" t="s">
+      <c r="E4" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="48"/>
-      <c r="G4" s="49" t="s">
+      <c r="F4" s="52"/>
+      <c r="G4" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="50" t="s">
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="51" t="s">
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="51"/>
-      <c r="S4" s="51"/>
-      <c r="T4" s="51"/>
-      <c r="U4" s="51"/>
-      <c r="V4" s="52" t="s">
+      <c r="R4" s="55"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="55"/>
+      <c r="U4" s="55"/>
+      <c r="V4" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="W4" s="52"/>
-      <c r="X4" s="52"/>
-      <c r="Y4" s="52"/>
+      <c r="W4" s="56"/>
+      <c r="X4" s="56"/>
+      <c r="Y4" s="56"/>
     </row>
     <row r="5" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1329,12 +1337,12 @@
       </c>
     </row>
     <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
       <c r="E6" s="7" t="s">
         <v>31</v>
       </c>
@@ -1400,12 +1408,12 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="11" t="s">
         <v>31</v>
       </c>
@@ -1459,33 +1467,33 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="44"/>
-      <c r="P8" s="44"/>
-      <c r="Q8" s="44"/>
-      <c r="R8" s="44"/>
-      <c r="S8" s="44"/>
-      <c r="T8" s="44"/>
-      <c r="U8" s="44"/>
-      <c r="V8" s="44"/>
-      <c r="W8" s="44"/>
-      <c r="X8" s="44"/>
-      <c r="Y8" s="44"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="48"/>
+      <c r="X8" s="48"/>
+      <c r="Y8" s="48"/>
     </row>
     <row r="9" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
@@ -1500,66 +1508,66 @@
       <c r="D9" s="17">
         <v>5</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="38"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="21"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="20"/>
-      <c r="Y9" s="19"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="18"/>
+      <c r="W9" s="18"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="18"/>
     </row>
     <row r="10" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
+      <c r="A10" s="21">
         <v>2</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="23">
         <v>6</v>
       </c>
-      <c r="E10" s="25"/>
-      <c r="F10" s="37" t="s">
+      <c r="E10" s="24"/>
+      <c r="F10" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="20"/>
-      <c r="T10" s="21"/>
-      <c r="U10" s="21"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="20"/>
-      <c r="Y10" s="25"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="24"/>
     </row>
     <row r="11" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
@@ -1574,64 +1582,64 @@
       <c r="D11" s="17">
         <v>7</v>
       </c>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="37" t="s">
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="21"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="20"/>
-      <c r="Y11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="18"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="18"/>
     </row>
     <row r="12" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="45"/>
-      <c r="O12" s="45"/>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="45"/>
-      <c r="R12" s="45"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="45"/>
-      <c r="U12" s="45"/>
-      <c r="V12" s="45"/>
-      <c r="W12" s="45"/>
-      <c r="X12" s="45"/>
-      <c r="Y12" s="45"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="49"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="49"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="49"/>
+      <c r="W12" s="49"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49"/>
     </row>
     <row r="13" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>4</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="25" t="s">
         <v>58</v>
       </c>
       <c r="C13" s="16" t="s">
@@ -1640,72 +1648,72 @@
       <c r="D13" s="17">
         <v>3.5</v>
       </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="39" t="s">
+      <c r="E13" s="18"/>
+      <c r="F13" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="20"/>
-      <c r="Y13" s="19"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="18"/>
+      <c r="W13" s="18"/>
+      <c r="X13" s="19"/>
+      <c r="Y13" s="18"/>
     </row>
     <row r="14" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+      <c r="A14" s="21">
         <v>5</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="23">
         <v>4</v>
       </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="27" t="s">
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="L14" s="28"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="25"/>
-      <c r="S14" s="20"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="21"/>
-      <c r="V14" s="25"/>
-      <c r="W14" s="25"/>
-      <c r="X14" s="20"/>
-      <c r="Y14" s="25"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="19"/>
+      <c r="Y14" s="24"/>
     </row>
     <row r="15" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>6</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="25" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="16" t="s">
@@ -1714,35 +1722,35 @@
       <c r="D15" s="17">
         <v>5.5</v>
       </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="27" t="s">
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="28"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="20"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="19"/>
-      <c r="X15" s="20"/>
-      <c r="Y15" s="19"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="18"/>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="18"/>
     </row>
     <row r="16" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>7</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="25" t="s">
         <v>58</v>
       </c>
       <c r="C16" s="16" t="s">
@@ -1751,72 +1759,72 @@
       <c r="D16" s="17">
         <v>7</v>
       </c>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="27" t="s">
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="N16" s="20"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="21"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="19"/>
-      <c r="X16" s="20"/>
-      <c r="Y16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="18"/>
+      <c r="W16" s="18"/>
+      <c r="X16" s="19"/>
+      <c r="Y16" s="18"/>
     </row>
     <row r="17" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22">
+      <c r="A17" s="21">
         <v>8</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="23">
         <v>7</v>
       </c>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="60" t="s">
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="P17" s="28"/>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="28"/>
-      <c r="S17" s="20"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="21"/>
-      <c r="V17" s="25"/>
-      <c r="W17" s="25"/>
-      <c r="X17" s="20"/>
-      <c r="Y17" s="25"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="27"/>
+      <c r="R17" s="27"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="24"/>
+      <c r="W17" s="24"/>
+      <c r="X17" s="19"/>
+      <c r="Y17" s="24"/>
     </row>
     <row r="18" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>9</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="25" t="s">
         <v>58</v>
       </c>
       <c r="C18" s="16" t="s">
@@ -1825,64 +1833,64 @@
       <c r="D18" s="17">
         <v>7.5</v>
       </c>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="27" t="s">
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="18"/>
+      <c r="R18" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="S18" s="20"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="21"/>
-      <c r="V18" s="28"/>
-      <c r="W18" s="28"/>
-      <c r="X18" s="20"/>
-      <c r="Y18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="27"/>
+      <c r="W18" s="27"/>
+      <c r="X18" s="19"/>
+      <c r="Y18" s="18"/>
     </row>
     <row r="19" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="53" t="s">
+      <c r="A19" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="53"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="53"/>
-      <c r="P19" s="53"/>
-      <c r="Q19" s="53"/>
-      <c r="R19" s="53"/>
-      <c r="S19" s="53"/>
-      <c r="T19" s="53"/>
-      <c r="U19" s="53"/>
-      <c r="V19" s="53"/>
-      <c r="W19" s="53"/>
-      <c r="X19" s="53"/>
-      <c r="Y19" s="53"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
     </row>
     <row r="20" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>10</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="29" t="s">
         <v>68</v>
       </c>
       <c r="C20" s="16" t="s">
@@ -1891,230 +1899,231 @@
       <c r="D20" s="17">
         <v>4.5</v>
       </c>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="20"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
-      <c r="V20" s="31" t="s">
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="W20" s="32"/>
-      <c r="X20" s="20"/>
-      <c r="Y20" s="19"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="19"/>
+      <c r="Y20" s="18"/>
     </row>
     <row r="21" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="22">
+      <c r="A21" s="21">
         <v>11</v>
       </c>
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="23">
         <v>9</v>
       </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="25"/>
-      <c r="P21" s="25"/>
-      <c r="Q21" s="25"/>
-      <c r="R21" s="25"/>
-      <c r="S21" s="20"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="31" t="s">
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
+      <c r="R21" s="24"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="W21" s="32"/>
-      <c r="X21" s="20"/>
-      <c r="Y21" s="32"/>
+      <c r="W21" s="31"/>
+      <c r="X21" s="19"/>
+      <c r="Y21" s="31"/>
     </row>
     <row r="22" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="22">
+      <c r="A22" s="21">
         <v>12</v>
       </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="40"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="40"/>
-      <c r="P22" s="40"/>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="40"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
-      <c r="V22" s="40"/>
-      <c r="W22" s="40"/>
-      <c r="X22" s="20"/>
-      <c r="Y22" s="40"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="38"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="38"/>
+      <c r="R22" s="38"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="38"/>
+      <c r="W22" s="38"/>
+      <c r="X22" s="19"/>
+      <c r="Y22" s="38"/>
     </row>
     <row r="23" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="58" t="s">
+      <c r="A23" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="58"/>
-      <c r="O23" s="58"/>
-      <c r="P23" s="58"/>
-      <c r="Q23" s="58"/>
-      <c r="R23" s="58"/>
-      <c r="S23" s="58"/>
-      <c r="T23" s="58"/>
-      <c r="U23" s="58"/>
-      <c r="V23" s="58"/>
-      <c r="W23" s="58"/>
-      <c r="X23" s="58"/>
-      <c r="Y23" s="58"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="62"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="62"/>
+      <c r="P23" s="62"/>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="62"/>
+      <c r="S23" s="62"/>
+      <c r="T23" s="62"/>
+      <c r="U23" s="62"/>
+      <c r="V23" s="62"/>
+      <c r="W23" s="62"/>
+      <c r="X23" s="62"/>
+      <c r="Y23" s="62"/>
     </row>
     <row r="24" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>13</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="23">
         <v>1</v>
       </c>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
-      <c r="N24" s="20"/>
-      <c r="P24" s="25"/>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="25"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="21"/>
-      <c r="U24" s="21"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="20"/>
-      <c r="Y24" s="19"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="24"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="24"/>
+      <c r="P24" s="24"/>
+      <c r="Q24" s="24"/>
+      <c r="R24" s="24"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="18"/>
+      <c r="X24" s="19"/>
+      <c r="Y24" s="18"/>
     </row>
     <row r="25" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>14</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="41">
+      <c r="D25" s="39">
         <v>1</v>
       </c>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="40"/>
-      <c r="M25" s="40"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="61" t="s">
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="P25" s="40"/>
-      <c r="Q25" s="40"/>
-      <c r="R25" s="40"/>
-      <c r="S25" s="20"/>
-      <c r="T25" s="21"/>
-      <c r="U25" s="21"/>
-      <c r="V25" s="40"/>
-      <c r="W25" s="40"/>
-      <c r="X25" s="20"/>
-      <c r="Y25" s="40"/>
+      <c r="P25" s="38"/>
+      <c r="Q25" s="38"/>
+      <c r="R25" s="38"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="20"/>
+      <c r="V25" s="38"/>
+      <c r="W25" s="38"/>
+      <c r="X25" s="19"/>
+      <c r="Y25" s="38"/>
     </row>
     <row r="26" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="54" t="s">
+      <c r="A26" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="55"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="55"/>
-      <c r="K26" s="55"/>
-      <c r="L26" s="55"/>
-      <c r="M26" s="55"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="55"/>
-      <c r="P26" s="55"/>
-      <c r="Q26" s="55"/>
-      <c r="R26" s="55"/>
-      <c r="S26" s="55"/>
-      <c r="T26" s="55"/>
-      <c r="U26" s="55"/>
-      <c r="V26" s="55"/>
-      <c r="W26" s="55"/>
-      <c r="X26" s="55"/>
-      <c r="Y26" s="55"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="59"/>
+      <c r="O26" s="59"/>
+      <c r="P26" s="59"/>
+      <c r="Q26" s="59"/>
+      <c r="R26" s="59"/>
+      <c r="S26" s="59"/>
+      <c r="T26" s="59"/>
+      <c r="U26" s="59"/>
+      <c r="V26" s="59"/>
+      <c r="W26" s="59"/>
+      <c r="X26" s="59"/>
+      <c r="Y26" s="59"/>
     </row>
     <row r="27" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>15</v>
       </c>
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="32" t="s">
         <v>73</v>
       </c>
       <c r="C27" s="16" t="s">
@@ -2123,37 +2132,37 @@
       <c r="D27" s="17">
         <v>22</v>
       </c>
-      <c r="E27" s="34" t="s">
+      <c r="E27" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="21"/>
-      <c r="U27" s="21"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="35"/>
-      <c r="X27" s="20"/>
-      <c r="Y27" s="35"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="33"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="19"/>
+      <c r="Y27" s="33"/>
     </row>
     <row r="28" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
-      <c r="B28" s="36" t="s">
+      <c r="A28" s="34"/>
+      <c r="B28" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36">
+      <c r="C28" s="34"/>
+      <c r="D28" s="34">
         <f>SUM(D8:D27)</f>
         <v>90</v>
       </c>
@@ -2180,58 +2189,58 @@
       <c r="Y28" s="1"/>
     </row>
     <row r="30" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="56"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="56"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="56"/>
-      <c r="M30" s="56"/>
-      <c r="N30" s="56"/>
-      <c r="O30" s="56"/>
-      <c r="P30" s="56"/>
-      <c r="Q30" s="56"/>
-      <c r="R30" s="56"/>
-      <c r="S30" s="56"/>
-      <c r="T30" s="56"/>
-      <c r="U30" s="56"/>
-      <c r="V30" s="56"/>
-      <c r="W30" s="56"/>
-      <c r="X30" s="56"/>
-      <c r="Y30" s="56"/>
+      <c r="A30" s="60"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="60"/>
+      <c r="K30" s="60"/>
+      <c r="L30" s="60"/>
+      <c r="M30" s="60"/>
+      <c r="N30" s="60"/>
+      <c r="O30" s="60"/>
+      <c r="P30" s="60"/>
+      <c r="Q30" s="60"/>
+      <c r="R30" s="60"/>
+      <c r="S30" s="60"/>
+      <c r="T30" s="60"/>
+      <c r="U30" s="60"/>
+      <c r="V30" s="60"/>
+      <c r="W30" s="60"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="60"/>
     </row>
     <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="57"/>
-      <c r="B31" s="57"/>
-      <c r="C31" s="57"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="57"/>
-      <c r="L31" s="57"/>
-      <c r="M31" s="57"/>
-      <c r="N31" s="57"/>
-      <c r="O31" s="57"/>
-      <c r="P31" s="57"/>
-      <c r="Q31" s="57"/>
-      <c r="R31" s="57"/>
-      <c r="S31" s="57"/>
-      <c r="T31" s="57"/>
-      <c r="U31" s="57"/>
-      <c r="V31" s="57"/>
-      <c r="W31" s="57"/>
-      <c r="X31" s="57"/>
-      <c r="Y31" s="57"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="61"/>
+      <c r="N31" s="61"/>
+      <c r="O31" s="61"/>
+      <c r="P31" s="61"/>
+      <c r="Q31" s="61"/>
+      <c r="R31" s="61"/>
+      <c r="S31" s="61"/>
+      <c r="T31" s="61"/>
+      <c r="U31" s="61"/>
+      <c r="V31" s="61"/>
+      <c r="W31" s="61"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
+++ b/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7D5259-5917-4CD4-8F63-18EBA4CFADBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36B6199-7EDF-4743-AEDF-F82053AB5560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planning Gantt" sheetId="1" r:id="rId1"/>
@@ -834,6 +834,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -863,24 +881,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1164,62 +1164,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
     </row>
     <row r="2" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="57"/>
+      <c r="T2" s="57"/>
+      <c r="U2" s="57"/>
+      <c r="V2" s="57"/>
+      <c r="W2" s="57"/>
+      <c r="X2" s="57"/>
+      <c r="Y2" s="57"/>
     </row>
     <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1227,37 +1227,37 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="52" t="s">
+      <c r="E4" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53" t="s">
+      <c r="F4" s="58"/>
+      <c r="G4" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="54" t="s">
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="55" t="s">
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
+      <c r="O4" s="60"/>
+      <c r="P4" s="60"/>
+      <c r="Q4" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="55"/>
-      <c r="U4" s="55"/>
-      <c r="V4" s="56" t="s">
+      <c r="R4" s="61"/>
+      <c r="S4" s="61"/>
+      <c r="T4" s="61"/>
+      <c r="U4" s="61"/>
+      <c r="V4" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="W4" s="56"/>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="56"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="62"/>
+      <c r="Y4" s="62"/>
     </row>
     <row r="5" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1337,12 +1337,12 @@
       </c>
     </row>
     <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="7" t="s">
         <v>31</v>
       </c>
@@ -1408,12 +1408,12 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="11" t="s">
         <v>31</v>
       </c>
@@ -1467,33 +1467,33 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
-      <c r="N8" s="48"/>
-      <c r="O8" s="48"/>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="48"/>
-      <c r="R8" s="48"/>
-      <c r="S8" s="48"/>
-      <c r="T8" s="48"/>
-      <c r="U8" s="48"/>
-      <c r="V8" s="48"/>
-      <c r="W8" s="48"/>
-      <c r="X8" s="48"/>
-      <c r="Y8" s="48"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="54"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="54"/>
+      <c r="R8" s="54"/>
+      <c r="S8" s="54"/>
+      <c r="T8" s="54"/>
+      <c r="U8" s="54"/>
+      <c r="V8" s="54"/>
+      <c r="W8" s="54"/>
+      <c r="X8" s="54"/>
+      <c r="Y8" s="54"/>
     </row>
     <row r="9" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
@@ -1607,33 +1607,33 @@
       <c r="Y11" s="18"/>
     </row>
     <row r="12" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="49"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="49"/>
-      <c r="P12" s="49"/>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="49"/>
-      <c r="W12" s="49"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="55"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="55"/>
+      <c r="P12" s="55"/>
+      <c r="Q12" s="55"/>
+      <c r="R12" s="55"/>
+      <c r="S12" s="55"/>
+      <c r="T12" s="55"/>
+      <c r="U12" s="55"/>
+      <c r="V12" s="55"/>
+      <c r="W12" s="55"/>
+      <c r="X12" s="55"/>
+      <c r="Y12" s="55"/>
     </row>
     <row r="13" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
@@ -1694,7 +1694,7 @@
       <c r="K14" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="L14" s="27"/>
+      <c r="L14" s="40"/>
       <c r="M14" s="24"/>
       <c r="N14" s="19"/>
       <c r="O14" s="24"/>
@@ -1729,10 +1729,10 @@
       <c r="I15" s="19"/>
       <c r="J15" s="18"/>
       <c r="K15" s="18"/>
-      <c r="L15" s="26" t="s">
+      <c r="L15" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="27"/>
+      <c r="M15" s="40"/>
       <c r="N15" s="19"/>
       <c r="O15" s="27"/>
       <c r="P15" s="18"/>
@@ -1767,7 +1767,7 @@
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
-      <c r="M16" s="26" t="s">
+      <c r="M16" s="37" t="s">
         <v>54</v>
       </c>
       <c r="N16" s="19"/>
@@ -1858,33 +1858,33 @@
       <c r="Y18" s="18"/>
     </row>
     <row r="19" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="57"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="47"/>
+      <c r="Q19" s="47"/>
+      <c r="R19" s="47"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="47"/>
+      <c r="V19" s="47"/>
+      <c r="W19" s="47"/>
+      <c r="X19" s="47"/>
+      <c r="Y19" s="47"/>
     </row>
     <row r="20" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
@@ -1990,33 +1990,33 @@
       <c r="Y22" s="38"/>
     </row>
     <row r="23" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="62"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="62"/>
-      <c r="T23" s="62"/>
-      <c r="U23" s="62"/>
-      <c r="V23" s="62"/>
-      <c r="W23" s="62"/>
-      <c r="X23" s="62"/>
-      <c r="Y23" s="62"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="52"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="52"/>
+      <c r="O23" s="52"/>
+      <c r="P23" s="52"/>
+      <c r="Q23" s="52"/>
+      <c r="R23" s="52"/>
+      <c r="S23" s="52"/>
+      <c r="T23" s="52"/>
+      <c r="U23" s="52"/>
+      <c r="V23" s="52"/>
+      <c r="W23" s="52"/>
+      <c r="X23" s="52"/>
+      <c r="Y23" s="52"/>
     </row>
     <row r="24" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
@@ -2091,33 +2091,33 @@
       <c r="Y25" s="38"/>
     </row>
     <row r="26" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="58" t="s">
+      <c r="A26" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="59"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="59"/>
-      <c r="O26" s="59"/>
-      <c r="P26" s="59"/>
-      <c r="Q26" s="59"/>
-      <c r="R26" s="59"/>
-      <c r="S26" s="59"/>
-      <c r="T26" s="59"/>
-      <c r="U26" s="59"/>
-      <c r="V26" s="59"/>
-      <c r="W26" s="59"/>
-      <c r="X26" s="59"/>
-      <c r="Y26" s="59"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="49"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="49"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="49"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="49"/>
+      <c r="T26" s="49"/>
+      <c r="U26" s="49"/>
+      <c r="V26" s="49"/>
+      <c r="W26" s="49"/>
+      <c r="X26" s="49"/>
+      <c r="Y26" s="49"/>
     </row>
     <row r="27" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
@@ -2189,66 +2189,61 @@
       <c r="Y28" s="1"/>
     </row>
     <row r="30" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="60"/>
-      <c r="B30" s="60"/>
-      <c r="C30" s="60"/>
-      <c r="D30" s="60"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="60"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="60"/>
-      <c r="J30" s="60"/>
-      <c r="K30" s="60"/>
-      <c r="L30" s="60"/>
-      <c r="M30" s="60"/>
-      <c r="N30" s="60"/>
-      <c r="O30" s="60"/>
-      <c r="P30" s="60"/>
-      <c r="Q30" s="60"/>
-      <c r="R30" s="60"/>
-      <c r="S30" s="60"/>
-      <c r="T30" s="60"/>
-      <c r="U30" s="60"/>
-      <c r="V30" s="60"/>
-      <c r="W30" s="60"/>
-      <c r="X30" s="60"/>
-      <c r="Y30" s="60"/>
+      <c r="A30" s="50"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="50"/>
+      <c r="M30" s="50"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="50"/>
+      <c r="P30" s="50"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="50"/>
+      <c r="S30" s="50"/>
+      <c r="T30" s="50"/>
+      <c r="U30" s="50"/>
+      <c r="V30" s="50"/>
+      <c r="W30" s="50"/>
+      <c r="X30" s="50"/>
+      <c r="Y30" s="50"/>
     </row>
     <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="61"/>
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="61"/>
-      <c r="N31" s="61"/>
-      <c r="O31" s="61"/>
-      <c r="P31" s="61"/>
-      <c r="Q31" s="61"/>
-      <c r="R31" s="61"/>
-      <c r="S31" s="61"/>
-      <c r="T31" s="61"/>
-      <c r="U31" s="61"/>
-      <c r="V31" s="61"/>
-      <c r="W31" s="61"/>
-      <c r="X31" s="61"/>
-      <c r="Y31" s="61"/>
+      <c r="A31" s="51"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="51"/>
+      <c r="L31" s="51"/>
+      <c r="M31" s="51"/>
+      <c r="N31" s="51"/>
+      <c r="O31" s="51"/>
+      <c r="P31" s="51"/>
+      <c r="Q31" s="51"/>
+      <c r="R31" s="51"/>
+      <c r="S31" s="51"/>
+      <c r="T31" s="51"/>
+      <c r="U31" s="51"/>
+      <c r="V31" s="51"/>
+      <c r="W31" s="51"/>
+      <c r="X31" s="51"/>
+      <c r="Y31" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A19:Y19"/>
-    <mergeCell ref="A26:Y26"/>
-    <mergeCell ref="A30:Y30"/>
-    <mergeCell ref="A31:Y31"/>
-    <mergeCell ref="A23:Y23"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A8:Y8"/>
@@ -2260,6 +2255,11 @@
     <mergeCell ref="L4:P4"/>
     <mergeCell ref="Q4:U4"/>
     <mergeCell ref="V4:Y4"/>
+    <mergeCell ref="A19:Y19"/>
+    <mergeCell ref="A26:Y26"/>
+    <mergeCell ref="A30:Y30"/>
+    <mergeCell ref="A31:Y31"/>
+    <mergeCell ref="A23:Y23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
+++ b/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36B6199-7EDF-4743-AEDF-F82053AB5560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF811E36-377F-4989-AD1E-0662231E7609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planning Gantt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="81">
   <si>
     <t>23–24 avr</t>
   </si>
@@ -308,7 +308,10 @@
     <t>TPI - Serial Guard v2  |  Planning initial</t>
   </si>
   <si>
-    <t>Visite du 2ème expert (Dimirios Lymberis) le jeudi 7 mai à 9h</t>
+    <t>Visite du 2ème expert monsieur Benzonana</t>
+  </si>
+  <si>
+    <t>Users management (CRUD si admin et gestion des roles), recherche des par username</t>
   </si>
 </sst>
 </file>
@@ -823,9 +826,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -834,6 +834,39 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -851,36 +884,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1153,7 +1156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:Y32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1164,62 +1167,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
     </row>
     <row r="2" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
-      <c r="Y2" s="57"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
     </row>
     <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1227,37 +1230,37 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="58" t="s">
+      <c r="E4" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="58"/>
-      <c r="G4" s="59" t="s">
+      <c r="F4" s="52"/>
+      <c r="G4" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="59"/>
-      <c r="L4" s="60" t="s">
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="61" t="s">
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="61"/>
-      <c r="S4" s="61"/>
-      <c r="T4" s="61"/>
-      <c r="U4" s="61"/>
-      <c r="V4" s="62" t="s">
+      <c r="R4" s="55"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="55"/>
+      <c r="U4" s="55"/>
+      <c r="V4" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="W4" s="62"/>
-      <c r="X4" s="62"/>
-      <c r="Y4" s="62"/>
+      <c r="W4" s="56"/>
+      <c r="X4" s="56"/>
+      <c r="Y4" s="56"/>
     </row>
     <row r="5" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1337,12 +1340,12 @@
       </c>
     </row>
     <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
       <c r="E6" s="7" t="s">
         <v>31</v>
       </c>
@@ -1408,12 +1411,12 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="11" t="s">
         <v>31</v>
       </c>
@@ -1467,33 +1470,33 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="54"/>
-      <c r="N8" s="54"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="54"/>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="54"/>
-      <c r="S8" s="54"/>
-      <c r="T8" s="54"/>
-      <c r="U8" s="54"/>
-      <c r="V8" s="54"/>
-      <c r="W8" s="54"/>
-      <c r="X8" s="54"/>
-      <c r="Y8" s="54"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="48"/>
+      <c r="X8" s="48"/>
+      <c r="Y8" s="48"/>
     </row>
     <row r="9" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
@@ -1590,7 +1593,7 @@
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="36"/>
-      <c r="K11" s="44"/>
+      <c r="K11" s="43"/>
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
       <c r="N11" s="19"/>
@@ -1607,33 +1610,33 @@
       <c r="Y11" s="18"/>
     </row>
     <row r="12" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="55"/>
-      <c r="N12" s="55"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="55"/>
-      <c r="R12" s="55"/>
-      <c r="S12" s="55"/>
-      <c r="T12" s="55"/>
-      <c r="U12" s="55"/>
-      <c r="V12" s="55"/>
-      <c r="W12" s="55"/>
-      <c r="X12" s="55"/>
-      <c r="Y12" s="55"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="49"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="49"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="49"/>
+      <c r="W12" s="49"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49"/>
     </row>
     <row r="13" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
@@ -1734,7 +1737,7 @@
       </c>
       <c r="M15" s="40"/>
       <c r="N15" s="19"/>
-      <c r="O15" s="27"/>
+      <c r="O15" s="40"/>
       <c r="P15" s="18"/>
       <c r="Q15" s="18"/>
       <c r="R15" s="18"/>
@@ -1771,8 +1774,8 @@
         <v>54</v>
       </c>
       <c r="N16" s="19"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="27"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="40"/>
       <c r="Q16" s="27"/>
       <c r="R16" s="18"/>
       <c r="S16" s="19"/>
@@ -1794,7 +1797,7 @@
         <v>65</v>
       </c>
       <c r="D17" s="23">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
@@ -1806,10 +1809,10 @@
       <c r="L17" s="24"/>
       <c r="M17" s="24"/>
       <c r="N17" s="19"/>
-      <c r="O17" s="42" t="s">
+      <c r="O17" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="P17" s="27"/>
+      <c r="P17" s="40"/>
       <c r="Q17" s="27"/>
       <c r="R17" s="27"/>
       <c r="S17" s="19"/>
@@ -1821,135 +1824,131 @@
       <c r="Y17" s="24"/>
     </row>
     <row r="18" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14">
-        <v>9</v>
-      </c>
+      <c r="A18" s="21"/>
       <c r="B18" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="17">
-        <v>7.5</v>
-      </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
+      <c r="C18" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="23">
+        <v>5</v>
+      </c>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
       <c r="I18" s="19"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="19"/>
-      <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="18"/>
-      <c r="R18" s="26" t="s">
-        <v>54</v>
-      </c>
+      <c r="O18" s="46"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="27"/>
+      <c r="R18" s="27"/>
       <c r="S18" s="19"/>
       <c r="T18" s="20"/>
       <c r="U18" s="20"/>
-      <c r="V18" s="27"/>
-      <c r="W18" s="27"/>
+      <c r="V18" s="24"/>
+      <c r="W18" s="24"/>
       <c r="X18" s="19"/>
-      <c r="Y18" s="18"/>
-    </row>
-    <row r="19" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="47" t="s">
+      <c r="Y18" s="24"/>
+    </row>
+    <row r="19" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14">
+        <v>9</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="17">
+        <v>7.5</v>
+      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="S19" s="19"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="27"/>
+      <c r="W19" s="27"/>
+      <c r="X19" s="19"/>
+      <c r="Y19" s="18"/>
+    </row>
+    <row r="20" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
-      <c r="P19" s="47"/>
-      <c r="Q19" s="47"/>
-      <c r="R19" s="47"/>
-      <c r="S19" s="47"/>
-      <c r="T19" s="47"/>
-      <c r="U19" s="47"/>
-      <c r="V19" s="47"/>
-      <c r="W19" s="47"/>
-      <c r="X19" s="47"/>
-      <c r="Y19" s="47"/>
-    </row>
-    <row r="20" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="14">
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="57"/>
+      <c r="P20" s="57"/>
+      <c r="Q20" s="57"/>
+      <c r="R20" s="57"/>
+      <c r="S20" s="57"/>
+      <c r="T20" s="57"/>
+      <c r="U20" s="57"/>
+      <c r="V20" s="57"/>
+      <c r="W20" s="57"/>
+      <c r="X20" s="57"/>
+      <c r="Y20" s="57"/>
+    </row>
+    <row r="21" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
         <v>10</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="17">
-        <v>4.5</v>
-      </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="18"/>
-      <c r="R20" s="18"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="20"/>
-      <c r="U20" s="20"/>
-      <c r="V20" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="W20" s="31"/>
-      <c r="X20" s="19"/>
-      <c r="Y20" s="18"/>
-    </row>
-    <row r="21" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="21">
-        <v>11</v>
       </c>
       <c r="B21" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="23">
-        <v>9</v>
-      </c>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
+      <c r="C21" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="17">
+        <v>4.5</v>
+      </c>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
       <c r="I21" s="19"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
       <c r="N21" s="19"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
       <c r="S21" s="19"/>
       <c r="T21" s="20"/>
       <c r="U21" s="20"/>
@@ -1958,292 +1957,333 @@
       </c>
       <c r="W21" s="31"/>
       <c r="X21" s="19"/>
-      <c r="Y21" s="31"/>
+      <c r="Y21" s="18"/>
     </row>
     <row r="22" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="21">
-        <v>12</v>
-      </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
+        <v>11</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="23">
+        <v>9</v>
+      </c>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
       <c r="I22" s="19"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="19"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="38"/>
-      <c r="R22" s="38"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
       <c r="S22" s="19"/>
       <c r="T22" s="20"/>
       <c r="U22" s="20"/>
-      <c r="V22" s="38"/>
-      <c r="W22" s="38"/>
+      <c r="V22" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="W22" s="31"/>
       <c r="X22" s="19"/>
-      <c r="Y22" s="38"/>
+      <c r="Y22" s="31"/>
     </row>
     <row r="23" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="21">
+        <v>12</v>
+      </c>
+      <c r="B23" s="29"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="38"/>
+      <c r="W23" s="38"/>
+      <c r="X23" s="19"/>
+      <c r="Y23" s="38"/>
+    </row>
+    <row r="24" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="52"/>
-      <c r="L23" s="52"/>
-      <c r="M23" s="52"/>
-      <c r="N23" s="52"/>
-      <c r="O23" s="52"/>
-      <c r="P23" s="52"/>
-      <c r="Q23" s="52"/>
-      <c r="R23" s="52"/>
-      <c r="S23" s="52"/>
-      <c r="T23" s="52"/>
-      <c r="U23" s="52"/>
-      <c r="V23" s="52"/>
-      <c r="W23" s="52"/>
-      <c r="X23" s="52"/>
-      <c r="Y23" s="52"/>
-    </row>
-    <row r="24" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="14">
-        <v>13</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" s="23">
-        <v>1</v>
-      </c>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="24"/>
-      <c r="Q24" s="24"/>
-      <c r="R24" s="24"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="20"/>
-      <c r="U24" s="20"/>
-      <c r="V24" s="18"/>
-      <c r="W24" s="18"/>
-      <c r="X24" s="19"/>
-      <c r="Y24" s="18"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="62"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="62"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="62"/>
+      <c r="P24" s="62"/>
+      <c r="Q24" s="62"/>
+      <c r="R24" s="62"/>
+      <c r="S24" s="62"/>
+      <c r="T24" s="62"/>
+      <c r="U24" s="62"/>
+      <c r="V24" s="62"/>
+      <c r="W24" s="62"/>
+      <c r="X24" s="62"/>
+      <c r="Y24" s="62"/>
     </row>
     <row r="25" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" s="39">
+        <v>63</v>
+      </c>
+      <c r="D25" s="23">
         <v>1</v>
       </c>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
       <c r="I25" s="19"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="24"/>
       <c r="N25" s="19"/>
-      <c r="O25" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="38"/>
-      <c r="R25" s="38"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
       <c r="S25" s="19"/>
       <c r="T25" s="20"/>
       <c r="U25" s="20"/>
-      <c r="V25" s="38"/>
-      <c r="W25" s="38"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="18"/>
       <c r="X25" s="19"/>
-      <c r="Y25" s="38"/>
-    </row>
-    <row r="26" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="48" t="s">
+      <c r="Y25" s="18"/>
+    </row>
+    <row r="26" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14">
+        <v>14</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="39">
+        <v>1</v>
+      </c>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="19"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="R26" s="38"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="20"/>
+      <c r="V26" s="38"/>
+      <c r="W26" s="38"/>
+      <c r="X26" s="19"/>
+      <c r="Y26" s="38"/>
+    </row>
+    <row r="27" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="49"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="49"/>
-      <c r="O26" s="49"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="49"/>
-      <c r="R26" s="49"/>
-      <c r="S26" s="49"/>
-      <c r="T26" s="49"/>
-      <c r="U26" s="49"/>
-      <c r="V26" s="49"/>
-      <c r="W26" s="49"/>
-      <c r="X26" s="49"/>
-      <c r="Y26" s="49"/>
-    </row>
-    <row r="27" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="14">
+      <c r="B27" s="59"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="59"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="59"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="59"/>
+      <c r="O27" s="59"/>
+      <c r="P27" s="59"/>
+      <c r="Q27" s="59"/>
+      <c r="R27" s="59"/>
+      <c r="S27" s="59"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="59"/>
+      <c r="V27" s="59"/>
+      <c r="W27" s="59"/>
+      <c r="X27" s="59"/>
+      <c r="Y27" s="59"/>
+    </row>
+    <row r="28" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14">
         <v>15</v>
       </c>
-      <c r="B27" s="32" t="s">
+      <c r="B28" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C28" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D28" s="17">
         <v>22</v>
       </c>
-      <c r="E27" s="45" t="s">
+      <c r="E28" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="33"/>
-      <c r="S27" s="19"/>
-      <c r="T27" s="20"/>
-      <c r="U27" s="20"/>
-      <c r="V27" s="33"/>
-      <c r="W27" s="33"/>
-      <c r="X27" s="19"/>
-      <c r="Y27" s="33"/>
-    </row>
-    <row r="28" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="34" t="s">
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="33"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="19"/>
+      <c r="Y28" s="33"/>
+    </row>
+    <row r="29" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="34"/>
+      <c r="B29" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34">
-        <f>SUM(D8:D27)</f>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34">
+        <f>SUM(D8:D28)</f>
         <v>90</v>
       </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-    </row>
-    <row r="30" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="50"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="50"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="50"/>
-      <c r="P30" s="50"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="50"/>
-      <c r="S30" s="50"/>
-      <c r="T30" s="50"/>
-      <c r="U30" s="50"/>
-      <c r="V30" s="50"/>
-      <c r="W30" s="50"/>
-      <c r="X30" s="50"/>
-      <c r="Y30" s="50"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
     </row>
     <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="51"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
-      <c r="K31" s="51"/>
-      <c r="L31" s="51"/>
-      <c r="M31" s="51"/>
-      <c r="N31" s="51"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="51"/>
-      <c r="R31" s="51"/>
-      <c r="S31" s="51"/>
-      <c r="T31" s="51"/>
-      <c r="U31" s="51"/>
-      <c r="V31" s="51"/>
-      <c r="W31" s="51"/>
-      <c r="X31" s="51"/>
-      <c r="Y31" s="51"/>
+      <c r="A31" s="60"/>
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="60"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="60"/>
+      <c r="T31" s="60"/>
+      <c r="U31" s="60"/>
+      <c r="V31" s="60"/>
+      <c r="W31" s="60"/>
+      <c r="X31" s="60"/>
+      <c r="Y31" s="60"/>
+    </row>
+    <row r="32" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="61"/>
+      <c r="B32" s="61"/>
+      <c r="C32" s="61"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="61"/>
+      <c r="N32" s="61"/>
+      <c r="O32" s="61"/>
+      <c r="P32" s="61"/>
+      <c r="Q32" s="61"/>
+      <c r="R32" s="61"/>
+      <c r="S32" s="61"/>
+      <c r="T32" s="61"/>
+      <c r="U32" s="61"/>
+      <c r="V32" s="61"/>
+      <c r="W32" s="61"/>
+      <c r="X32" s="61"/>
+      <c r="Y32" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A20:Y20"/>
+    <mergeCell ref="A27:Y27"/>
+    <mergeCell ref="A31:Y31"/>
+    <mergeCell ref="A32:Y32"/>
+    <mergeCell ref="A24:Y24"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A8:Y8"/>
@@ -2255,11 +2295,6 @@
     <mergeCell ref="L4:P4"/>
     <mergeCell ref="Q4:U4"/>
     <mergeCell ref="V4:Y4"/>
-    <mergeCell ref="A19:Y19"/>
-    <mergeCell ref="A26:Y26"/>
-    <mergeCell ref="A30:Y30"/>
-    <mergeCell ref="A31:Y31"/>
-    <mergeCell ref="A23:Y23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
+++ b/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF811E36-377F-4989-AD1E-0662231E7609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5BF999-53D4-4017-A65E-14D85B429232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planning Gantt" sheetId="1" r:id="rId1"/>
@@ -261,10 +261,6 @@
 CRUD, types, statuts étendus, recherche S/N + type, assignation, garanties, export CSV</t>
   </si>
   <si>
-    <t>OCR  —  ajout par scan
-Upload image → Tesseract, extraction S/N, approbation, gestion erreurs</t>
-  </si>
-  <si>
     <t>Logs &amp; messages d'erreur
 Table logs, log_action(), page admin logs, filtres, messages validation</t>
   </si>
@@ -311,14 +307,18 @@
     <t>Visite du 2ème expert monsieur Benzonana</t>
   </si>
   <si>
-    <t>Users management (CRUD si admin et gestion des roles), recherche des par username</t>
+    <t>OCR - ajout par scan
+Upload image → Tesseract, extraction S/N, approbation, gestion erreurs</t>
+  </si>
+  <si>
+    <t>Users management (CRUD si admin et gestion des roles), recherche des users par username</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -441,6 +441,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1E2A38"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -625,12 +631,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD7BDE2"/>
-        <bgColor rgb="FFF8F8F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC3EFEC"/>
         <bgColor rgb="FFB3E5FC"/>
       </patternFill>
@@ -639,6 +639,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF42ACD2"/>
         <bgColor rgb="FFA8D8EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB685C9"/>
+        <bgColor rgb="FFF8F8F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -721,7 +727,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -826,15 +832,18 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -960,6 +969,7 @@
     </indexedColors>
     <mruColors>
       <color rgb="FF42ACD2"/>
+      <color rgb="FFB685C9"/>
       <color rgb="FFC3EFEC"/>
       <color rgb="FF65D5CD"/>
       <color rgb="FFD7BDE2"/>
@@ -1167,62 +1177,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
+      <c r="A1" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+      <c r="W1" s="51"/>
+      <c r="X1" s="51"/>
+      <c r="Y1" s="51"/>
     </row>
     <row r="2" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
+      <c r="A2" s="52" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
     </row>
     <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1230,37 +1240,37 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="52" t="s">
+      <c r="E4" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53" t="s">
+      <c r="F4" s="53"/>
+      <c r="G4" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="54" t="s">
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="55" t="s">
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="55"/>
-      <c r="U4" s="55"/>
-      <c r="V4" s="56" t="s">
+      <c r="R4" s="56"/>
+      <c r="S4" s="56"/>
+      <c r="T4" s="56"/>
+      <c r="U4" s="56"/>
+      <c r="V4" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="W4" s="56"/>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="56"/>
+      <c r="W4" s="57"/>
+      <c r="X4" s="57"/>
+      <c r="Y4" s="57"/>
     </row>
     <row r="5" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1340,12 +1350,12 @@
       </c>
     </row>
     <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
       <c r="E6" s="7" t="s">
         <v>31</v>
       </c>
@@ -1411,12 +1421,12 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
       <c r="E7" s="11" t="s">
         <v>31</v>
       </c>
@@ -1470,33 +1480,33 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
-      <c r="N8" s="48"/>
-      <c r="O8" s="48"/>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="48"/>
-      <c r="R8" s="48"/>
-      <c r="S8" s="48"/>
-      <c r="T8" s="48"/>
-      <c r="U8" s="48"/>
-      <c r="V8" s="48"/>
-      <c r="W8" s="48"/>
-      <c r="X8" s="48"/>
-      <c r="Y8" s="48"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="49"/>
+      <c r="T8" s="49"/>
+      <c r="U8" s="49"/>
+      <c r="V8" s="49"/>
+      <c r="W8" s="49"/>
+      <c r="X8" s="49"/>
+      <c r="Y8" s="49"/>
     </row>
     <row r="9" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
@@ -1593,7 +1603,7 @@
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="36"/>
-      <c r="K11" s="43"/>
+      <c r="K11" s="42"/>
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
       <c r="N11" s="19"/>
@@ -1610,33 +1620,33 @@
       <c r="Y11" s="18"/>
     </row>
     <row r="12" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="49"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="49"/>
-      <c r="P12" s="49"/>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="49"/>
-      <c r="W12" s="49"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="50"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
     </row>
     <row r="13" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
@@ -1776,7 +1786,7 @@
       <c r="N16" s="19"/>
       <c r="O16" s="40"/>
       <c r="P16" s="40"/>
-      <c r="Q16" s="27"/>
+      <c r="Q16" s="40"/>
       <c r="R16" s="18"/>
       <c r="S16" s="19"/>
       <c r="T16" s="20"/>
@@ -1794,7 +1804,7 @@
         <v>58</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D17" s="23">
         <v>2</v>
@@ -1809,12 +1819,12 @@
       <c r="L17" s="24"/>
       <c r="M17" s="24"/>
       <c r="N17" s="19"/>
-      <c r="O17" s="46" t="s">
+      <c r="O17" s="45" t="s">
         <v>54</v>
       </c>
       <c r="P17" s="40"/>
-      <c r="Q17" s="27"/>
-      <c r="R17" s="27"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="40"/>
       <c r="S17" s="19"/>
       <c r="T17" s="20"/>
       <c r="U17" s="20"/>
@@ -1828,7 +1838,7 @@
       <c r="B18" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="46" t="s">
         <v>80</v>
       </c>
       <c r="D18" s="23">
@@ -1844,10 +1854,10 @@
       <c r="L18" s="24"/>
       <c r="M18" s="24"/>
       <c r="N18" s="19"/>
-      <c r="O18" s="46"/>
+      <c r="O18" s="45"/>
       <c r="P18" s="40"/>
-      <c r="Q18" s="27"/>
-      <c r="R18" s="27"/>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="40"/>
       <c r="S18" s="19"/>
       <c r="T18" s="20"/>
       <c r="U18" s="20"/>
@@ -1864,7 +1874,7 @@
         <v>58</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D19" s="17">
         <v>7.5</v>
@@ -1894,43 +1904,43 @@
       <c r="Y19" s="18"/>
     </row>
     <row r="20" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="57"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="57"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="57"/>
-      <c r="P20" s="57"/>
-      <c r="Q20" s="57"/>
-      <c r="R20" s="57"/>
-      <c r="S20" s="57"/>
-      <c r="T20" s="57"/>
-      <c r="U20" s="57"/>
-      <c r="V20" s="57"/>
-      <c r="W20" s="57"/>
-      <c r="X20" s="57"/>
-      <c r="Y20" s="57"/>
+      <c r="A20" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="58"/>
+      <c r="P20" s="58"/>
+      <c r="Q20" s="58"/>
+      <c r="R20" s="58"/>
+      <c r="S20" s="58"/>
+      <c r="T20" s="58"/>
+      <c r="U20" s="58"/>
+      <c r="V20" s="58"/>
+      <c r="W20" s="58"/>
+      <c r="X20" s="58"/>
+      <c r="Y20" s="58"/>
     </row>
     <row r="21" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>10</v>
       </c>
       <c r="B21" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>68</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>69</v>
       </c>
       <c r="D21" s="17">
         <v>4.5</v>
@@ -1964,10 +1974,10 @@
         <v>11</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D22" s="23">
         <v>9</v>
@@ -2026,40 +2036,40 @@
       <c r="Y23" s="38"/>
     </row>
     <row r="24" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="62" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="62"/>
-      <c r="M24" s="62"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="62"/>
-      <c r="P24" s="62"/>
-      <c r="Q24" s="62"/>
-      <c r="R24" s="62"/>
-      <c r="S24" s="62"/>
-      <c r="T24" s="62"/>
-      <c r="U24" s="62"/>
-      <c r="V24" s="62"/>
-      <c r="W24" s="62"/>
-      <c r="X24" s="62"/>
-      <c r="Y24" s="62"/>
+      <c r="A24" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="63"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="63"/>
+      <c r="K24" s="63"/>
+      <c r="L24" s="63"/>
+      <c r="M24" s="63"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="63"/>
+      <c r="P24" s="63"/>
+      <c r="Q24" s="63"/>
+      <c r="R24" s="63"/>
+      <c r="S24" s="63"/>
+      <c r="T24" s="63"/>
+      <c r="U24" s="63"/>
+      <c r="V24" s="63"/>
+      <c r="W24" s="63"/>
+      <c r="X24" s="63"/>
+      <c r="Y24" s="63"/>
     </row>
     <row r="25" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>13</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C25" s="41" t="s">
         <v>63</v>
@@ -2097,7 +2107,7 @@
         <v>62</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D26" s="39">
         <v>1</v>
@@ -2113,7 +2123,7 @@
       <c r="M26" s="38"/>
       <c r="N26" s="19"/>
       <c r="P26" s="38"/>
-      <c r="Q26" s="42" t="s">
+      <c r="Q26" s="47" t="s">
         <v>54</v>
       </c>
       <c r="R26" s="38"/>
@@ -2126,56 +2136,56 @@
       <c r="Y26" s="38"/>
     </row>
     <row r="27" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="58" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27" s="59"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="59"/>
-      <c r="J27" s="59"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="59"/>
-      <c r="M27" s="59"/>
-      <c r="N27" s="59"/>
-      <c r="O27" s="59"/>
-      <c r="P27" s="59"/>
-      <c r="Q27" s="59"/>
-      <c r="R27" s="59"/>
-      <c r="S27" s="59"/>
-      <c r="T27" s="59"/>
-      <c r="U27" s="59"/>
-      <c r="V27" s="59"/>
-      <c r="W27" s="59"/>
-      <c r="X27" s="59"/>
-      <c r="Y27" s="59"/>
+      <c r="A27" s="59" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="60"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="60"/>
+      <c r="K27" s="60"/>
+      <c r="L27" s="60"/>
+      <c r="M27" s="60"/>
+      <c r="N27" s="60"/>
+      <c r="O27" s="60"/>
+      <c r="P27" s="60"/>
+      <c r="Q27" s="60"/>
+      <c r="R27" s="60"/>
+      <c r="S27" s="60"/>
+      <c r="T27" s="60"/>
+      <c r="U27" s="60"/>
+      <c r="V27" s="60"/>
+      <c r="W27" s="60"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="60"/>
     </row>
     <row r="28" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>15</v>
       </c>
       <c r="B28" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="16" t="s">
         <v>73</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>74</v>
       </c>
       <c r="D28" s="17">
         <v>22</v>
       </c>
-      <c r="E28" s="44" t="s">
+      <c r="E28" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
       <c r="I28" s="19"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="45"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="44"/>
       <c r="L28" s="33"/>
       <c r="M28" s="33"/>
       <c r="N28" s="19"/>
@@ -2194,7 +2204,7 @@
     <row r="29" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="34"/>
       <c r="B29" s="34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C29" s="34"/>
       <c r="D29" s="34">
@@ -2224,58 +2234,58 @@
       <c r="Y29" s="1"/>
     </row>
     <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="60"/>
-      <c r="B31" s="60"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="60"/>
-      <c r="J31" s="60"/>
-      <c r="K31" s="60"/>
-      <c r="L31" s="60"/>
-      <c r="M31" s="60"/>
-      <c r="N31" s="60"/>
-      <c r="O31" s="60"/>
-      <c r="P31" s="60"/>
-      <c r="Q31" s="60"/>
-      <c r="R31" s="60"/>
-      <c r="S31" s="60"/>
-      <c r="T31" s="60"/>
-      <c r="U31" s="60"/>
-      <c r="V31" s="60"/>
-      <c r="W31" s="60"/>
-      <c r="X31" s="60"/>
-      <c r="Y31" s="60"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="61"/>
+      <c r="N31" s="61"/>
+      <c r="O31" s="61"/>
+      <c r="P31" s="61"/>
+      <c r="Q31" s="61"/>
+      <c r="R31" s="61"/>
+      <c r="S31" s="61"/>
+      <c r="T31" s="61"/>
+      <c r="U31" s="61"/>
+      <c r="V31" s="61"/>
+      <c r="W31" s="61"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="61"/>
     </row>
     <row r="32" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="61"/>
-      <c r="B32" s="61"/>
-      <c r="C32" s="61"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="61"/>
-      <c r="N32" s="61"/>
-      <c r="O32" s="61"/>
-      <c r="P32" s="61"/>
-      <c r="Q32" s="61"/>
-      <c r="R32" s="61"/>
-      <c r="S32" s="61"/>
-      <c r="T32" s="61"/>
-      <c r="U32" s="61"/>
-      <c r="V32" s="61"/>
-      <c r="W32" s="61"/>
-      <c r="X32" s="61"/>
-      <c r="Y32" s="61"/>
+      <c r="A32" s="62"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="62"/>
+      <c r="L32" s="62"/>
+      <c r="M32" s="62"/>
+      <c r="N32" s="62"/>
+      <c r="O32" s="62"/>
+      <c r="P32" s="62"/>
+      <c r="Q32" s="62"/>
+      <c r="R32" s="62"/>
+      <c r="S32" s="62"/>
+      <c r="T32" s="62"/>
+      <c r="U32" s="62"/>
+      <c r="V32" s="62"/>
+      <c r="W32" s="62"/>
+      <c r="X32" s="62"/>
+      <c r="Y32" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
+++ b/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5BF999-53D4-4017-A65E-14D85B429232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F83FB0C-0A23-4E32-B42F-84A566CCF071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -846,6 +846,24 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -875,24 +893,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1177,62 +1177,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+      <c r="U1" s="57"/>
+      <c r="V1" s="57"/>
+      <c r="W1" s="57"/>
+      <c r="X1" s="57"/>
+      <c r="Y1" s="57"/>
     </row>
     <row r="2" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
-      <c r="V2" s="52"/>
-      <c r="W2" s="52"/>
-      <c r="X2" s="52"/>
-      <c r="Y2" s="52"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="58"/>
+      <c r="S2" s="58"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="58"/>
+      <c r="V2" s="58"/>
+      <c r="W2" s="58"/>
+      <c r="X2" s="58"/>
+      <c r="Y2" s="58"/>
     </row>
     <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1240,37 +1240,37 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="53"/>
-      <c r="G4" s="54" t="s">
+      <c r="F4" s="59"/>
+      <c r="G4" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="55" t="s">
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="56" t="s">
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="57" t="s">
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="W4" s="57"/>
-      <c r="X4" s="57"/>
-      <c r="Y4" s="57"/>
+      <c r="W4" s="63"/>
+      <c r="X4" s="63"/>
+      <c r="Y4" s="63"/>
     </row>
     <row r="5" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1350,12 +1350,12 @@
       </c>
     </row>
     <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
       <c r="E6" s="7" t="s">
         <v>31</v>
       </c>
@@ -1421,12 +1421,12 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
       <c r="E7" s="11" t="s">
         <v>31</v>
       </c>
@@ -1480,33 +1480,33 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49"/>
-      <c r="P8" s="49"/>
-      <c r="Q8" s="49"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="49"/>
-      <c r="U8" s="49"/>
-      <c r="V8" s="49"/>
-      <c r="W8" s="49"/>
-      <c r="X8" s="49"/>
-      <c r="Y8" s="49"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="55"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="55"/>
+      <c r="Q8" s="55"/>
+      <c r="R8" s="55"/>
+      <c r="S8" s="55"/>
+      <c r="T8" s="55"/>
+      <c r="U8" s="55"/>
+      <c r="V8" s="55"/>
+      <c r="W8" s="55"/>
+      <c r="X8" s="55"/>
+      <c r="Y8" s="55"/>
     </row>
     <row r="9" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
@@ -1620,33 +1620,33 @@
       <c r="Y11" s="18"/>
     </row>
     <row r="12" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="50"/>
-      <c r="V12" s="50"/>
-      <c r="W12" s="50"/>
-      <c r="X12" s="50"/>
-      <c r="Y12" s="50"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="56"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="56"/>
+      <c r="M12" s="56"/>
+      <c r="N12" s="56"/>
+      <c r="O12" s="56"/>
+      <c r="P12" s="56"/>
+      <c r="Q12" s="56"/>
+      <c r="R12" s="56"/>
+      <c r="S12" s="56"/>
+      <c r="T12" s="56"/>
+      <c r="U12" s="56"/>
+      <c r="V12" s="56"/>
+      <c r="W12" s="56"/>
+      <c r="X12" s="56"/>
+      <c r="Y12" s="56"/>
     </row>
     <row r="13" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
@@ -1898,39 +1898,39 @@
       <c r="S19" s="19"/>
       <c r="T19" s="20"/>
       <c r="U19" s="20"/>
-      <c r="V19" s="27"/>
+      <c r="V19" s="40"/>
       <c r="W19" s="27"/>
       <c r="X19" s="19"/>
       <c r="Y19" s="18"/>
     </row>
     <row r="20" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="58" t="s">
+      <c r="A20" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="58"/>
-      <c r="O20" s="58"/>
-      <c r="P20" s="58"/>
-      <c r="Q20" s="58"/>
-      <c r="R20" s="58"/>
-      <c r="S20" s="58"/>
-      <c r="T20" s="58"/>
-      <c r="U20" s="58"/>
-      <c r="V20" s="58"/>
-      <c r="W20" s="58"/>
-      <c r="X20" s="58"/>
-      <c r="Y20" s="58"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="48"/>
+      <c r="L20" s="48"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="48"/>
+      <c r="O20" s="48"/>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="48"/>
+      <c r="R20" s="48"/>
+      <c r="S20" s="48"/>
+      <c r="T20" s="48"/>
+      <c r="U20" s="48"/>
+      <c r="V20" s="48"/>
+      <c r="W20" s="48"/>
+      <c r="X20" s="48"/>
+      <c r="Y20" s="48"/>
     </row>
     <row r="21" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
@@ -2036,33 +2036,33 @@
       <c r="Y23" s="38"/>
     </row>
     <row r="24" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="63" t="s">
+      <c r="A24" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="63"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="63"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="63"/>
-      <c r="M24" s="63"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="63"/>
-      <c r="P24" s="63"/>
-      <c r="Q24" s="63"/>
-      <c r="R24" s="63"/>
-      <c r="S24" s="63"/>
-      <c r="T24" s="63"/>
-      <c r="U24" s="63"/>
-      <c r="V24" s="63"/>
-      <c r="W24" s="63"/>
-      <c r="X24" s="63"/>
-      <c r="Y24" s="63"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="53"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
+      <c r="R24" s="53"/>
+      <c r="S24" s="53"/>
+      <c r="T24" s="53"/>
+      <c r="U24" s="53"/>
+      <c r="V24" s="53"/>
+      <c r="W24" s="53"/>
+      <c r="X24" s="53"/>
+      <c r="Y24" s="53"/>
     </row>
     <row r="25" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
@@ -2136,33 +2136,33 @@
       <c r="Y26" s="38"/>
     </row>
     <row r="27" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="59" t="s">
+      <c r="A27" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="B27" s="60"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="60"/>
-      <c r="J27" s="60"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="60"/>
-      <c r="M27" s="60"/>
-      <c r="N27" s="60"/>
-      <c r="O27" s="60"/>
-      <c r="P27" s="60"/>
-      <c r="Q27" s="60"/>
-      <c r="R27" s="60"/>
-      <c r="S27" s="60"/>
-      <c r="T27" s="60"/>
-      <c r="U27" s="60"/>
-      <c r="V27" s="60"/>
-      <c r="W27" s="60"/>
-      <c r="X27" s="60"/>
-      <c r="Y27" s="60"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="50"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="50"/>
+      <c r="O27" s="50"/>
+      <c r="P27" s="50"/>
+      <c r="Q27" s="50"/>
+      <c r="R27" s="50"/>
+      <c r="S27" s="50"/>
+      <c r="T27" s="50"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="50"/>
+      <c r="W27" s="50"/>
+      <c r="X27" s="50"/>
+      <c r="Y27" s="50"/>
     </row>
     <row r="28" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
@@ -2234,66 +2234,61 @@
       <c r="Y29" s="1"/>
     </row>
     <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="61"/>
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="61"/>
-      <c r="N31" s="61"/>
-      <c r="O31" s="61"/>
-      <c r="P31" s="61"/>
-      <c r="Q31" s="61"/>
-      <c r="R31" s="61"/>
-      <c r="S31" s="61"/>
-      <c r="T31" s="61"/>
-      <c r="U31" s="61"/>
-      <c r="V31" s="61"/>
-      <c r="W31" s="61"/>
-      <c r="X31" s="61"/>
-      <c r="Y31" s="61"/>
+      <c r="A31" s="51"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="51"/>
+      <c r="L31" s="51"/>
+      <c r="M31" s="51"/>
+      <c r="N31" s="51"/>
+      <c r="O31" s="51"/>
+      <c r="P31" s="51"/>
+      <c r="Q31" s="51"/>
+      <c r="R31" s="51"/>
+      <c r="S31" s="51"/>
+      <c r="T31" s="51"/>
+      <c r="U31" s="51"/>
+      <c r="V31" s="51"/>
+      <c r="W31" s="51"/>
+      <c r="X31" s="51"/>
+      <c r="Y31" s="51"/>
     </row>
     <row r="32" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="62"/>
-      <c r="B32" s="62"/>
-      <c r="C32" s="62"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="62"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="62"/>
-      <c r="L32" s="62"/>
-      <c r="M32" s="62"/>
-      <c r="N32" s="62"/>
-      <c r="O32" s="62"/>
-      <c r="P32" s="62"/>
-      <c r="Q32" s="62"/>
-      <c r="R32" s="62"/>
-      <c r="S32" s="62"/>
-      <c r="T32" s="62"/>
-      <c r="U32" s="62"/>
-      <c r="V32" s="62"/>
-      <c r="W32" s="62"/>
-      <c r="X32" s="62"/>
-      <c r="Y32" s="62"/>
+      <c r="A32" s="52"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="52"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="52"/>
+      <c r="O32" s="52"/>
+      <c r="P32" s="52"/>
+      <c r="Q32" s="52"/>
+      <c r="R32" s="52"/>
+      <c r="S32" s="52"/>
+      <c r="T32" s="52"/>
+      <c r="U32" s="52"/>
+      <c r="V32" s="52"/>
+      <c r="W32" s="52"/>
+      <c r="X32" s="52"/>
+      <c r="Y32" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A20:Y20"/>
-    <mergeCell ref="A27:Y27"/>
-    <mergeCell ref="A31:Y31"/>
-    <mergeCell ref="A32:Y32"/>
-    <mergeCell ref="A24:Y24"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A8:Y8"/>
@@ -2305,6 +2300,11 @@
     <mergeCell ref="L4:P4"/>
     <mergeCell ref="Q4:U4"/>
     <mergeCell ref="V4:Y4"/>
+    <mergeCell ref="A20:Y20"/>
+    <mergeCell ref="A27:Y27"/>
+    <mergeCell ref="A31:Y31"/>
+    <mergeCell ref="A32:Y32"/>
+    <mergeCell ref="A24:Y24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
+++ b/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F83FB0C-0A23-4E32-B42F-84A566CCF071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9255" yWindow="0" windowWidth="19650" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planning Gantt" sheetId="1" r:id="rId1"/>
@@ -846,6 +846,36 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -863,36 +893,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1177,62 +1177,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+      <c r="W1" s="51"/>
+      <c r="X1" s="51"/>
+      <c r="Y1" s="51"/>
     </row>
     <row r="2" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
-      <c r="Y2" s="58"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
     </row>
     <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1240,37 +1240,37 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="59" t="s">
+      <c r="E4" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="59"/>
-      <c r="G4" s="60" t="s">
+      <c r="F4" s="53"/>
+      <c r="G4" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="61" t="s">
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="61"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="62" t="s">
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="62"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="62"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="63" t="s">
+      <c r="R4" s="56"/>
+      <c r="S4" s="56"/>
+      <c r="T4" s="56"/>
+      <c r="U4" s="56"/>
+      <c r="V4" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="W4" s="63"/>
-      <c r="X4" s="63"/>
-      <c r="Y4" s="63"/>
+      <c r="W4" s="57"/>
+      <c r="X4" s="57"/>
+      <c r="Y4" s="57"/>
     </row>
     <row r="5" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1350,12 +1350,12 @@
       </c>
     </row>
     <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
       <c r="E6" s="7" t="s">
         <v>31</v>
       </c>
@@ -1421,12 +1421,12 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
       <c r="E7" s="11" t="s">
         <v>31</v>
       </c>
@@ -1480,33 +1480,33 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="55"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="55"/>
-      <c r="Q8" s="55"/>
-      <c r="R8" s="55"/>
-      <c r="S8" s="55"/>
-      <c r="T8" s="55"/>
-      <c r="U8" s="55"/>
-      <c r="V8" s="55"/>
-      <c r="W8" s="55"/>
-      <c r="X8" s="55"/>
-      <c r="Y8" s="55"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="49"/>
+      <c r="T8" s="49"/>
+      <c r="U8" s="49"/>
+      <c r="V8" s="49"/>
+      <c r="W8" s="49"/>
+      <c r="X8" s="49"/>
+      <c r="Y8" s="49"/>
     </row>
     <row r="9" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
@@ -1620,33 +1620,33 @@
       <c r="Y11" s="18"/>
     </row>
     <row r="12" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="56" t="s">
+      <c r="A12" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="56"/>
-      <c r="K12" s="56"/>
-      <c r="L12" s="56"/>
-      <c r="M12" s="56"/>
-      <c r="N12" s="56"/>
-      <c r="O12" s="56"/>
-      <c r="P12" s="56"/>
-      <c r="Q12" s="56"/>
-      <c r="R12" s="56"/>
-      <c r="S12" s="56"/>
-      <c r="T12" s="56"/>
-      <c r="U12" s="56"/>
-      <c r="V12" s="56"/>
-      <c r="W12" s="56"/>
-      <c r="X12" s="56"/>
-      <c r="Y12" s="56"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="50"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
     </row>
     <row r="13" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
@@ -1904,33 +1904,33 @@
       <c r="Y19" s="18"/>
     </row>
     <row r="20" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="48" t="s">
+      <c r="A20" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="48"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="48"/>
-      <c r="L20" s="48"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="48"/>
-      <c r="P20" s="48"/>
-      <c r="Q20" s="48"/>
-      <c r="R20" s="48"/>
-      <c r="S20" s="48"/>
-      <c r="T20" s="48"/>
-      <c r="U20" s="48"/>
-      <c r="V20" s="48"/>
-      <c r="W20" s="48"/>
-      <c r="X20" s="48"/>
-      <c r="Y20" s="48"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="58"/>
+      <c r="P20" s="58"/>
+      <c r="Q20" s="58"/>
+      <c r="R20" s="58"/>
+      <c r="S20" s="58"/>
+      <c r="T20" s="58"/>
+      <c r="U20" s="58"/>
+      <c r="V20" s="58"/>
+      <c r="W20" s="58"/>
+      <c r="X20" s="58"/>
+      <c r="Y20" s="58"/>
     </row>
     <row r="21" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
@@ -2036,33 +2036,33 @@
       <c r="Y23" s="38"/>
     </row>
     <row r="24" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="53" t="s">
+      <c r="A24" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="53"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53"/>
-      <c r="R24" s="53"/>
-      <c r="S24" s="53"/>
-      <c r="T24" s="53"/>
-      <c r="U24" s="53"/>
-      <c r="V24" s="53"/>
-      <c r="W24" s="53"/>
-      <c r="X24" s="53"/>
-      <c r="Y24" s="53"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="63"/>
+      <c r="K24" s="63"/>
+      <c r="L24" s="63"/>
+      <c r="M24" s="63"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="63"/>
+      <c r="P24" s="63"/>
+      <c r="Q24" s="63"/>
+      <c r="R24" s="63"/>
+      <c r="S24" s="63"/>
+      <c r="T24" s="63"/>
+      <c r="U24" s="63"/>
+      <c r="V24" s="63"/>
+      <c r="W24" s="63"/>
+      <c r="X24" s="63"/>
+      <c r="Y24" s="63"/>
     </row>
     <row r="25" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
@@ -2136,33 +2136,33 @@
       <c r="Y26" s="38"/>
     </row>
     <row r="27" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="50"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="50"/>
-      <c r="R27" s="50"/>
-      <c r="S27" s="50"/>
-      <c r="T27" s="50"/>
-      <c r="U27" s="50"/>
-      <c r="V27" s="50"/>
-      <c r="W27" s="50"/>
-      <c r="X27" s="50"/>
-      <c r="Y27" s="50"/>
+      <c r="B27" s="60"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="60"/>
+      <c r="K27" s="60"/>
+      <c r="L27" s="60"/>
+      <c r="M27" s="60"/>
+      <c r="N27" s="60"/>
+      <c r="O27" s="60"/>
+      <c r="P27" s="60"/>
+      <c r="Q27" s="60"/>
+      <c r="R27" s="60"/>
+      <c r="S27" s="60"/>
+      <c r="T27" s="60"/>
+      <c r="U27" s="60"/>
+      <c r="V27" s="60"/>
+      <c r="W27" s="60"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="60"/>
     </row>
     <row r="28" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
@@ -2234,61 +2234,66 @@
       <c r="Y29" s="1"/>
     </row>
     <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="51"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
-      <c r="K31" s="51"/>
-      <c r="L31" s="51"/>
-      <c r="M31" s="51"/>
-      <c r="N31" s="51"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="51"/>
-      <c r="R31" s="51"/>
-      <c r="S31" s="51"/>
-      <c r="T31" s="51"/>
-      <c r="U31" s="51"/>
-      <c r="V31" s="51"/>
-      <c r="W31" s="51"/>
-      <c r="X31" s="51"/>
-      <c r="Y31" s="51"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="61"/>
+      <c r="N31" s="61"/>
+      <c r="O31" s="61"/>
+      <c r="P31" s="61"/>
+      <c r="Q31" s="61"/>
+      <c r="R31" s="61"/>
+      <c r="S31" s="61"/>
+      <c r="T31" s="61"/>
+      <c r="U31" s="61"/>
+      <c r="V31" s="61"/>
+      <c r="W31" s="61"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="61"/>
     </row>
     <row r="32" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="52"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="52"/>
-      <c r="M32" s="52"/>
-      <c r="N32" s="52"/>
-      <c r="O32" s="52"/>
-      <c r="P32" s="52"/>
-      <c r="Q32" s="52"/>
-      <c r="R32" s="52"/>
-      <c r="S32" s="52"/>
-      <c r="T32" s="52"/>
-      <c r="U32" s="52"/>
-      <c r="V32" s="52"/>
-      <c r="W32" s="52"/>
-      <c r="X32" s="52"/>
-      <c r="Y32" s="52"/>
+      <c r="A32" s="62"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="62"/>
+      <c r="L32" s="62"/>
+      <c r="M32" s="62"/>
+      <c r="N32" s="62"/>
+      <c r="O32" s="62"/>
+      <c r="P32" s="62"/>
+      <c r="Q32" s="62"/>
+      <c r="R32" s="62"/>
+      <c r="S32" s="62"/>
+      <c r="T32" s="62"/>
+      <c r="U32" s="62"/>
+      <c r="V32" s="62"/>
+      <c r="W32" s="62"/>
+      <c r="X32" s="62"/>
+      <c r="Y32" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A20:Y20"/>
+    <mergeCell ref="A27:Y27"/>
+    <mergeCell ref="A31:Y31"/>
+    <mergeCell ref="A32:Y32"/>
+    <mergeCell ref="A24:Y24"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A8:Y8"/>
@@ -2300,11 +2305,6 @@
     <mergeCell ref="L4:P4"/>
     <mergeCell ref="Q4:U4"/>
     <mergeCell ref="V4:Y4"/>
-    <mergeCell ref="A20:Y20"/>
-    <mergeCell ref="A27:Y27"/>
-    <mergeCell ref="A31:Y31"/>
-    <mergeCell ref="A32:Y32"/>
-    <mergeCell ref="A24:Y24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
+++ b/Documents/LAM_Jimmy-planning-initial-TPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F83FB0C-0A23-4E32-B42F-84A566CCF071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695270E4-2A86-443F-BAF9-0CE0BBA96730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9255" yWindow="0" windowWidth="19650" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planning Gantt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="80">
   <si>
     <t>23–24 avr</t>
   </si>
@@ -252,9 +252,6 @@
   </si>
   <si>
     <t>2ème expert</t>
-  </si>
-  <si>
-    <t>Visite du 2ème expert  (à planifier)</t>
   </si>
   <si>
     <t>Gestion des équipements
@@ -448,7 +445,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -583,12 +580,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAD7A0"/>
-        <bgColor rgb="FFFADBD8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6AAEC6"/>
         <bgColor rgb="FF45B7D1"/>
       </patternFill>
@@ -645,6 +636,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFB685C9"/>
         <bgColor rgb="FFF8F8F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF185266"/>
+        <bgColor rgb="FFF8F8F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor rgb="FFFADBD8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor rgb="FFF8F8F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor rgb="FFFADBD8"/>
       </patternFill>
     </fill>
   </fills>
@@ -727,7 +742,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -797,29 +812,24 @@
     <xf numFmtId="0" fontId="12" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -828,23 +838,41 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -876,24 +904,13 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -968,6 +985,7 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FF185266"/>
       <color rgb="FF42ACD2"/>
       <color rgb="FFB685C9"/>
       <color rgb="FFC3EFEC"/>
@@ -1177,62 +1195,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
+      <c r="A1" s="54" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
     </row>
     <row r="2" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
-      <c r="V2" s="52"/>
-      <c r="W2" s="52"/>
-      <c r="X2" s="52"/>
-      <c r="Y2" s="52"/>
+      <c r="A2" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="55"/>
     </row>
     <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1240,37 +1258,37 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="53"/>
-      <c r="G4" s="54" t="s">
+      <c r="F4" s="56"/>
+      <c r="G4" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="55" t="s">
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="56" t="s">
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="57" t="s">
+      <c r="R4" s="59"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="59"/>
+      <c r="U4" s="59"/>
+      <c r="V4" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="W4" s="57"/>
-      <c r="X4" s="57"/>
-      <c r="Y4" s="57"/>
+      <c r="W4" s="60"/>
+      <c r="X4" s="60"/>
+      <c r="Y4" s="60"/>
     </row>
     <row r="5" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1350,12 +1368,12 @@
       </c>
     </row>
     <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="7" t="s">
         <v>31</v>
       </c>
@@ -1421,12 +1439,12 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="11" t="s">
         <v>31</v>
       </c>
@@ -1480,33 +1498,33 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49"/>
-      <c r="P8" s="49"/>
-      <c r="Q8" s="49"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="49"/>
-      <c r="U8" s="49"/>
-      <c r="V8" s="49"/>
-      <c r="W8" s="49"/>
-      <c r="X8" s="49"/>
-      <c r="Y8" s="49"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="52"/>
+      <c r="O8" s="52"/>
+      <c r="P8" s="52"/>
+      <c r="Q8" s="52"/>
+      <c r="R8" s="52"/>
+      <c r="S8" s="52"/>
+      <c r="T8" s="52"/>
+      <c r="U8" s="52"/>
+      <c r="V8" s="52"/>
+      <c r="W8" s="52"/>
+      <c r="X8" s="52"/>
+      <c r="Y8" s="52"/>
     </row>
     <row r="9" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
@@ -1521,10 +1539,10 @@
       <c r="D9" s="17">
         <v>5</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="36"/>
+      <c r="F9" s="33"/>
       <c r="G9" s="18"/>
       <c r="H9" s="18"/>
       <c r="I9" s="19"/>
@@ -1559,13 +1577,13 @@
         <v>6</v>
       </c>
       <c r="E10" s="24"/>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
       <c r="I10" s="19"/>
-      <c r="J10" s="36"/>
+      <c r="J10" s="33"/>
       <c r="K10" s="24"/>
       <c r="L10" s="24"/>
       <c r="M10" s="24"/>
@@ -1598,12 +1616,12 @@
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
-      <c r="H11" s="35" t="s">
+      <c r="H11" s="32" t="s">
         <v>54</v>
       </c>
       <c r="I11" s="19"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="42"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="39"/>
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
       <c r="N11" s="19"/>
@@ -1620,33 +1638,33 @@
       <c r="Y11" s="18"/>
     </row>
     <row r="12" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="50"/>
-      <c r="V12" s="50"/>
-      <c r="W12" s="50"/>
-      <c r="X12" s="50"/>
-      <c r="Y12" s="50"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
+      <c r="P12" s="53"/>
+      <c r="Q12" s="53"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="53"/>
+      <c r="T12" s="53"/>
+      <c r="U12" s="53"/>
+      <c r="V12" s="53"/>
+      <c r="W12" s="53"/>
+      <c r="X12" s="53"/>
+      <c r="Y12" s="53"/>
     </row>
     <row r="13" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
@@ -1662,14 +1680,14 @@
         <v>3.5</v>
       </c>
       <c r="E13" s="18"/>
-      <c r="F13" s="37" t="s">
+      <c r="F13" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="19"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="40"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
       <c r="L13" s="18"/>
       <c r="M13" s="18"/>
       <c r="N13" s="19"/>
@@ -1704,10 +1722,10 @@
       <c r="H14" s="24"/>
       <c r="I14" s="19"/>
       <c r="J14" s="24"/>
-      <c r="K14" s="37" t="s">
+      <c r="K14" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="L14" s="40"/>
+      <c r="L14" s="37"/>
       <c r="M14" s="24"/>
       <c r="N14" s="19"/>
       <c r="O14" s="24"/>
@@ -1742,12 +1760,12 @@
       <c r="I15" s="19"/>
       <c r="J15" s="18"/>
       <c r="K15" s="18"/>
-      <c r="L15" s="37" t="s">
+      <c r="L15" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="40"/>
+      <c r="M15" s="37"/>
       <c r="N15" s="19"/>
-      <c r="O15" s="40"/>
+      <c r="O15" s="37"/>
       <c r="P15" s="18"/>
       <c r="Q15" s="18"/>
       <c r="R15" s="18"/>
@@ -1767,7 +1785,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" s="17">
         <v>7</v>
@@ -1780,13 +1798,13 @@
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
-      <c r="M16" s="37" t="s">
+      <c r="M16" s="34" t="s">
         <v>54</v>
       </c>
       <c r="N16" s="19"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="40"/>
+      <c r="O16" s="37"/>
+      <c r="P16" s="37"/>
+      <c r="Q16" s="37"/>
       <c r="R16" s="18"/>
       <c r="S16" s="19"/>
       <c r="T16" s="20"/>
@@ -1804,7 +1822,7 @@
         <v>58</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D17" s="23">
         <v>2</v>
@@ -1819,12 +1837,12 @@
       <c r="L17" s="24"/>
       <c r="M17" s="24"/>
       <c r="N17" s="19"/>
-      <c r="O17" s="45" t="s">
+      <c r="O17" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="P17" s="40"/>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="40"/>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="37"/>
+      <c r="R17" s="37"/>
       <c r="S17" s="19"/>
       <c r="T17" s="20"/>
       <c r="U17" s="20"/>
@@ -1838,8 +1856,8 @@
       <c r="B18" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="46" t="s">
-        <v>80</v>
+      <c r="C18" s="43" t="s">
+        <v>79</v>
       </c>
       <c r="D18" s="23">
         <v>5</v>
@@ -1854,10 +1872,10 @@
       <c r="L18" s="24"/>
       <c r="M18" s="24"/>
       <c r="N18" s="19"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="40"/>
-      <c r="Q18" s="40"/>
-      <c r="R18" s="40"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="37"/>
+      <c r="Q18" s="37"/>
+      <c r="R18" s="37"/>
       <c r="S18" s="19"/>
       <c r="T18" s="20"/>
       <c r="U18" s="20"/>
@@ -1874,7 +1892,7 @@
         <v>58</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D19" s="17">
         <v>7.5</v>
@@ -1898,49 +1916,49 @@
       <c r="S19" s="19"/>
       <c r="T19" s="20"/>
       <c r="U19" s="20"/>
-      <c r="V19" s="40"/>
-      <c r="W19" s="27"/>
+      <c r="V19" s="37"/>
+      <c r="W19" s="37"/>
       <c r="X19" s="19"/>
-      <c r="Y19" s="18"/>
+      <c r="Y19" s="61"/>
     </row>
     <row r="20" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="58" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="58"/>
-      <c r="O20" s="58"/>
-      <c r="P20" s="58"/>
-      <c r="Q20" s="58"/>
-      <c r="R20" s="58"/>
-      <c r="S20" s="58"/>
-      <c r="T20" s="58"/>
-      <c r="U20" s="58"/>
-      <c r="V20" s="58"/>
-      <c r="W20" s="58"/>
-      <c r="X20" s="58"/>
-      <c r="Y20" s="58"/>
+      <c r="A20" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="45"/>
+      <c r="R20" s="45"/>
+      <c r="S20" s="45"/>
+      <c r="T20" s="45"/>
+      <c r="U20" s="45"/>
+      <c r="V20" s="45"/>
+      <c r="W20" s="45"/>
+      <c r="X20" s="45"/>
+      <c r="Y20" s="45"/>
     </row>
     <row r="21" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>10</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>67</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>68</v>
       </c>
       <c r="D21" s="17">
         <v>4.5</v>
@@ -1962,22 +1980,22 @@
       <c r="S21" s="19"/>
       <c r="T21" s="20"/>
       <c r="U21" s="20"/>
-      <c r="V21" s="30" t="s">
+      <c r="V21" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="W21" s="31"/>
+      <c r="W21" s="63"/>
       <c r="X21" s="19"/>
-      <c r="Y21" s="18"/>
+      <c r="Y21" s="64"/>
     </row>
     <row r="22" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="21">
         <v>11</v>
       </c>
-      <c r="B22" s="29" t="s">
-        <v>67</v>
+      <c r="B22" s="28" t="s">
+        <v>66</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D22" s="23">
         <v>9</v>
@@ -1999,81 +2017,79 @@
       <c r="S22" s="19"/>
       <c r="T22" s="20"/>
       <c r="U22" s="20"/>
-      <c r="V22" s="30" t="s">
+      <c r="V22" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="W22" s="31"/>
+      <c r="W22" s="63"/>
       <c r="X22" s="19"/>
-      <c r="Y22" s="31"/>
+      <c r="Y22" s="65"/>
     </row>
     <row r="23" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="21">
         <v>12</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
       <c r="I23" s="19"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
       <c r="N23" s="19"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-      <c r="R23" s="38"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
       <c r="S23" s="19"/>
       <c r="T23" s="20"/>
       <c r="U23" s="20"/>
-      <c r="V23" s="38"/>
-      <c r="W23" s="38"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="35"/>
       <c r="X23" s="19"/>
-      <c r="Y23" s="38"/>
+      <c r="Y23" s="35"/>
     </row>
     <row r="24" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="63" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="63"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="63"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="63"/>
-      <c r="M24" s="63"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="63"/>
-      <c r="P24" s="63"/>
-      <c r="Q24" s="63"/>
-      <c r="R24" s="63"/>
-      <c r="S24" s="63"/>
-      <c r="T24" s="63"/>
-      <c r="U24" s="63"/>
-      <c r="V24" s="63"/>
-      <c r="W24" s="63"/>
-      <c r="X24" s="63"/>
-      <c r="Y24" s="63"/>
+      <c r="A24" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="50"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="50"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="50"/>
+      <c r="O24" s="50"/>
+      <c r="P24" s="50"/>
+      <c r="Q24" s="50"/>
+      <c r="R24" s="50"/>
+      <c r="S24" s="50"/>
+      <c r="T24" s="50"/>
+      <c r="U24" s="50"/>
+      <c r="V24" s="50"/>
+      <c r="W24" s="50"/>
+      <c r="X24" s="50"/>
+      <c r="Y24" s="50"/>
     </row>
     <row r="25" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>13</v>
       </c>
-      <c r="B25" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>63</v>
-      </c>
+      <c r="B25" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="38"/>
       <c r="D25" s="23">
         <v>1</v>
       </c>
@@ -2103,111 +2119,111 @@
       <c r="A26" s="14">
         <v>14</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" s="39">
+      <c r="C26" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="36">
         <v>1</v>
       </c>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
       <c r="I26" s="19"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="38"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
       <c r="N26" s="19"/>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="47" t="s">
+      <c r="P26" s="35"/>
+      <c r="Q26" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="R26" s="38"/>
+      <c r="R26" s="35"/>
       <c r="S26" s="19"/>
       <c r="T26" s="20"/>
       <c r="U26" s="20"/>
-      <c r="V26" s="38"/>
-      <c r="W26" s="38"/>
+      <c r="V26" s="35"/>
+      <c r="W26" s="35"/>
       <c r="X26" s="19"/>
-      <c r="Y26" s="38"/>
+      <c r="Y26" s="35"/>
     </row>
     <row r="27" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="59" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="60"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="60"/>
-      <c r="J27" s="60"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="60"/>
-      <c r="M27" s="60"/>
-      <c r="N27" s="60"/>
-      <c r="O27" s="60"/>
-      <c r="P27" s="60"/>
-      <c r="Q27" s="60"/>
-      <c r="R27" s="60"/>
-      <c r="S27" s="60"/>
-      <c r="T27" s="60"/>
-      <c r="U27" s="60"/>
-      <c r="V27" s="60"/>
-      <c r="W27" s="60"/>
-      <c r="X27" s="60"/>
-      <c r="Y27" s="60"/>
+      <c r="A27" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="47"/>
+      <c r="N27" s="47"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="47"/>
+      <c r="Q27" s="47"/>
+      <c r="R27" s="47"/>
+      <c r="S27" s="47"/>
+      <c r="T27" s="47"/>
+      <c r="U27" s="47"/>
+      <c r="V27" s="47"/>
+      <c r="W27" s="47"/>
+      <c r="X27" s="47"/>
+      <c r="Y27" s="47"/>
     </row>
     <row r="28" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>15</v>
       </c>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="16" t="s">
         <v>72</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>73</v>
       </c>
       <c r="D28" s="17">
         <v>22</v>
       </c>
-      <c r="E28" s="43" t="s">
+      <c r="E28" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
       <c r="I28" s="19"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="44"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
       <c r="N28" s="19"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="33"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
       <c r="S28" s="19"/>
       <c r="T28" s="20"/>
       <c r="U28" s="20"/>
-      <c r="V28" s="33"/>
-      <c r="W28" s="33"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="30"/>
       <c r="X28" s="19"/>
-      <c r="Y28" s="33"/>
+      <c r="Y28" s="30"/>
     </row>
     <row r="29" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="B29" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34">
+      <c r="A29" s="31"/>
+      <c r="B29" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31">
         <f>SUM(D8:D28)</f>
         <v>90</v>
       </c>
@@ -2234,66 +2250,61 @@
       <c r="Y29" s="1"/>
     </row>
     <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="61"/>
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="61"/>
-      <c r="N31" s="61"/>
-      <c r="O31" s="61"/>
-      <c r="P31" s="61"/>
-      <c r="Q31" s="61"/>
-      <c r="R31" s="61"/>
-      <c r="S31" s="61"/>
-      <c r="T31" s="61"/>
-      <c r="U31" s="61"/>
-      <c r="V31" s="61"/>
-      <c r="W31" s="61"/>
-      <c r="X31" s="61"/>
-      <c r="Y31" s="61"/>
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="48"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="48"/>
+      <c r="O31" s="48"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="48"/>
+      <c r="R31" s="48"/>
+      <c r="S31" s="48"/>
+      <c r="T31" s="48"/>
+      <c r="U31" s="48"/>
+      <c r="V31" s="48"/>
+      <c r="W31" s="48"/>
+      <c r="X31" s="48"/>
+      <c r="Y31" s="48"/>
     </row>
     <row r="32" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="62"/>
-      <c r="B32" s="62"/>
-      <c r="C32" s="62"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="62"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="62"/>
-      <c r="L32" s="62"/>
-      <c r="M32" s="62"/>
-      <c r="N32" s="62"/>
-      <c r="O32" s="62"/>
-      <c r="P32" s="62"/>
-      <c r="Q32" s="62"/>
-      <c r="R32" s="62"/>
-      <c r="S32" s="62"/>
-      <c r="T32" s="62"/>
-      <c r="U32" s="62"/>
-      <c r="V32" s="62"/>
-      <c r="W32" s="62"/>
-      <c r="X32" s="62"/>
-      <c r="Y32" s="62"/>
+      <c r="A32" s="49"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="49"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+      <c r="L32" s="49"/>
+      <c r="M32" s="49"/>
+      <c r="N32" s="49"/>
+      <c r="O32" s="49"/>
+      <c r="P32" s="49"/>
+      <c r="Q32" s="49"/>
+      <c r="R32" s="49"/>
+      <c r="S32" s="49"/>
+      <c r="T32" s="49"/>
+      <c r="U32" s="49"/>
+      <c r="V32" s="49"/>
+      <c r="W32" s="49"/>
+      <c r="X32" s="49"/>
+      <c r="Y32" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A20:Y20"/>
-    <mergeCell ref="A27:Y27"/>
-    <mergeCell ref="A31:Y31"/>
-    <mergeCell ref="A32:Y32"/>
-    <mergeCell ref="A24:Y24"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A8:Y8"/>
@@ -2305,6 +2316,11 @@
     <mergeCell ref="L4:P4"/>
     <mergeCell ref="Q4:U4"/>
     <mergeCell ref="V4:Y4"/>
+    <mergeCell ref="A20:Y20"/>
+    <mergeCell ref="A27:Y27"/>
+    <mergeCell ref="A31:Y31"/>
+    <mergeCell ref="A32:Y32"/>
+    <mergeCell ref="A24:Y24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
